--- a/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
+++ b/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
@@ -535,6 +535,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_a09_1.csv</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>09-09_11-19-17_426_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -610,6 +620,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_a09_2.csv</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>09-09_11-21-27_792_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -685,6 +705,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_a10_1.csv</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>09-09_11-23-48_013_ExgCh1Data_(Frank 右脛前肌)_a10_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -760,6 +790,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>09-09_11-25-35_742_ExgCh1Data_(Frank 右脛前肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -835,6 +875,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_ze2_1.csv</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>09-09_11-27-57_319_Ch2_(Frank 右脛前肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -910,6 +960,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2609-09 frank右脛前肌(Delsys)_with_ze2_2.csv</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>09-09_11-30-01_689_Ch2_(Frank 右脛前肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -985,6 +1045,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_a09_1.csv</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>09-09_09-41-19_786_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1060,6 +1130,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_a09_2.csv</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>09-09_09-45-46_944_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1135,6 +1215,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_a10_1.csv</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>09-09_09-52-57_312_ExgCh2Data_(Frank 左脛前肌)_a10_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1210,6 +1300,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>09-09_09-58-36_663_ExgCh2Data_(Frank 左脛前肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1285,6 +1385,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_ze2_1.csv</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>09-09_10-8-56_879_Ch1_(Frank_左脛前肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1360,6 +1470,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2609-09 frank左脛前肌(Delsys)_with_ze2_2.csv</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>09-09_10-12-46_289_Ch1_(Frank 左脛前肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1435,6 +1555,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_a09_1.csv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>09-09_11-48-01_319_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1508,6 +1638,12 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>09-09_11-50-05_808_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_2.txt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1565,6 +1701,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_a10_1.csv</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>09-09_11-52-29_385_ExgCh2Data_(Frank 右腓腸肌)_a10_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1640,6 +1786,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>09-09_11-55-52_064_ExgCh2Data_(Frank 右腓腸肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1715,6 +1871,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_1.csv</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>09-09_11-59-10_048_Ch1_(Frank 右腓腸肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1790,6 +1956,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_2.csv</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>09-09_12-1-14_084_Ch1_(Frank 右腓腸肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1865,6 +2041,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_1.csv</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -1940,6 +2126,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_2.csv</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>09-09_10-35-51_625_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2015,6 +2211,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_1.csv</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>09-09_10-40-13_031_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2090,6 +2296,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>09-09_10-45-37_881_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2165,6 +2381,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_1.csv</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>09-09_10-48-41_826_Ch2_(Frank 左腓腸肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2240,6 +2466,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_2.csv</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>09-09_10-51-00_016_Ch2_(Frank 左腓腸肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2315,6 +2551,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>09-09_11-19-17_426_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>09-09_14-55-41_279_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2390,6 +2636,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>09-09_09-41-19_786_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>09-09_12-39-13_023_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2465,6 +2721,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>09-09_11-48-01_319_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>09-09_15-16-55_610_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2540,6 +2806,16 @@
           <t>3</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>09-09_14-32-12_387_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>3/3</t>
@@ -2615,6 +2891,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>09-09_14-57-46_856_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -2690,6 +2976,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -2765,6 +3061,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -2840,6 +3146,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -2915,6 +3231,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -2990,6 +3316,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3065,6 +3401,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3140,6 +3486,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3215,6 +3571,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3290,6 +3656,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3365,6 +3741,16 @@
           <t>10</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>10/10</t>
@@ -3438,6 +3824,16 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>09-09_14-42-34_881_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">

--- a/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
+++ b/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
@@ -507,8 +507,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -592,8 +594,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>3</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -677,8 +681,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -720,30 +726,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.5505</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0058</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.8007</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0174</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.5533</t>
-        </is>
+      <c r="J4" t="n">
+        <v>0.6493</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8706</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5121</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -762,8 +758,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>5</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -805,30 +803,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-0.8963</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-0.0088</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-0.8567</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>-0.0262</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.8032</t>
-        </is>
+      <c r="J5" t="n">
+        <v>-0.9321</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.8839</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7771</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -847,8 +835,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -932,8 +922,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>7</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1017,8 +1009,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>8</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1102,8 +1096,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>9</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1187,8 +1183,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>10</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1230,30 +1228,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-0.9597</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-0.0265</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-0.9978</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>-0.0106</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.2451</t>
-        </is>
+      <c r="J10" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.6435999999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5620000000000001</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1272,8 +1260,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>11</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1315,30 +1305,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.1823</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.0059</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-0.6747</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-0.1626</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.5189</t>
-        </is>
+      <c r="J11" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7377</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5523</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1357,8 +1337,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>12</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1442,8 +1424,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>13</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1527,8 +1511,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>14</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1612,8 +1598,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>15</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1673,8 +1661,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>16</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1716,2090 +1706,2100 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0.4625</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9962</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>09-09_11-55-52_064_ExgCh2Data_(Frank 右腓腸肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9056999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6568000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6901</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ze2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_1.csv</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>09-09_11-59-10_048_Ch1_(Frank 右腓腸肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.3058</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.0444</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.6406</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>0.0136</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-0.3862</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-0.0062</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-0.4293</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.6372</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>右腓腸肌</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>裝置比對</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ze2</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_2.csv</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>09-09_12-1-14_084_Ch1_(Frank 右腓腸肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.9522</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.1667</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.9393</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.0816</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.7142</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_1.csv</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.7192</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-1.3328</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.9813</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-1.1669</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-0.1774</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_2.csv</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>09-09_10-35-51_625_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_2.txt</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-0.9122</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-0.0962</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.9942</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.6884</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.2577</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>a10</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2609-09 frank右腓腸肌(Delsys)_with_a10_2.csv</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>09-09_11-55-52_064_ExgCh2Data_(Frank 右腓腸肌)_a10_褲XL_2.txt</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_1.csv</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>09-09_10-40-13_031_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0565</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>a10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_2.csv</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>09-09_10-45-37_881_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_2.txt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3/2</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.5228</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ze2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_1.csv</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>09-09_10-48-41_826_Ch2_(Frank 左腓腸肌)_ze2_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>3/3</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-0.576</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-0.0004</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-0.8292</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>-0.0018</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-0.206</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.9654</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.6655</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.9904</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0.8479</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0.4885</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>裝置比對</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ze2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_2.csv</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>09-09_10-51-00_016_Ch2_(Frank 左腓腸肌)_ze2_褲XL_2.txt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.6147</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.3277</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.3241</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.1419</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-0.5826</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>刮腿毛</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>09-09_11-19-17_426_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>09-09_14-55-41_279_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-0.996</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-0.3202</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-0.9545</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-1.0625</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0.6523</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>刮腿毛</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>09-09_09-41-19_786_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>09-09_12-39-13_023_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.9191</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0.1011</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.9768</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0.4132</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-0.525</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>右腓腸肌</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ze2</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>刮腿毛</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_1.csv</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>09-09_11-59-10_048_Ch1_(Frank 右腓腸肌)_ze2_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>09-09_11-48-01_319_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>09-09_15-16-55_610_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>3/3</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-0.3058</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-0.0444</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.6406</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0.0136</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-0.6372</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-0.9381</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-0.0371</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.9944</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0.0756</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0.5324</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>刮腿毛</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>09-09_14-32-12_387_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_去腿毛.txt</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-0.9979</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-0.4554</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0.1333</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>09-09_14-57-46_856_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.3741</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.0834</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.2904</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.1762</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-0.2449</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.8488</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0.3082</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.7219</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>-0.4582</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-0.3006</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.381</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0.2759</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0.256</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>-0.1208</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-0.073</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.9457</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0.8447</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.8562</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>0.757</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0.7313</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.8149</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0.7833</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0.6955</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0.6878</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.9049</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.7679</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0.7283</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0.6903</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0.6993</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>右腓腸肌</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ze2</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2609-09 frank右腓腸肌(Delsys)_with_ZE2_2.csv</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>09-09_12-1-14_084_Ch1_(Frank 右腓腸肌)_ze2_褲XL_2.txt</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.9522</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.1667</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.9393</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>0.0816</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0.7142</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.5929</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0.0209</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0.1875</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>0.0179</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-0.3697</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.8102</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0.0216</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0.4873</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0.0802</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-0.3552</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.6024</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0.0042</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0.7273</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0.3049</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>左腓腸肌</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_1.csv</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-0.7192</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-1.3328</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-0.9813</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-1.1669</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-0.1774</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>21</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.7612</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.2252</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.7976</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0.4027</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-0.1084</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>左腓腸肌</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_a09_2.csv</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>09-09_10-35-51_625_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_2.txt</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-0.9122</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-0.0962</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.9942</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>0.6884</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.2577</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>a10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_1.csv</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>09-09_10-40-13_031_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0.9682</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.0973</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0.9939</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>0.1219</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0.1243</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>23</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>a10</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_a10_2.csv</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>09-09_10-45-37_881_ExgCh1Data_(Frank 左腓腸肌)_a10_褲XL_2.txt</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0.6576</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.0201</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>0.8457</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>0.0696</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>0.1515</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>24</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ze2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_1.csv</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>09-09_10-48-41_826_Ch2_(Frank 左腓腸肌)_ze2_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0.9654</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.6655</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0.9904</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>0.8479</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.4885</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>裝置比對</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ze2</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2609-09 frank左腓腸肌(Delsys)_with_ze2_2.csv</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>09-09_10-51-00_016_Ch2_(Frank 左腓腸肌)_ze2_褲XL_2.txt</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0.6147</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.3277</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0.3241</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>0.1419</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-0.5826</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>刮腿毛</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>09-09_11-19-17_426_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>09-09_14-55-41_279_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_去腿毛.txt</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-0.996</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-0.3202</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-0.9545</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>-1.0625</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0.6523</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>刮腿毛</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>09-09_09-41-19_786_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>09-09_12-39-13_023_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_去腿毛.txt</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.9191</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.1011</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.9768</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-0.525</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>28</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>刮腿毛</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>09-09_11-48-01_319_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>09-09_15-16-55_610_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_去腿毛.txt</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-0.9381</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-0.0371</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.9944</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>0.0756</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0.5324</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>29</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>刮腿毛</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>09-09_10-31-15_181_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_1.txt</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>09-09_14-32-12_387_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_去腿毛.txt</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3/3</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>-0.9979</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>-0.4554</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0.1333</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>疲勞</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>09-09_14-57-46_856_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0.3741</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.0834</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0.2904</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>0.1762</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-0.2449</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.7245</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.3198</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0.6036</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0.6176</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0.1626</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>31</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0.8488</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.3082</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>-0.7219</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>-0.4582</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-0.3006</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>32</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0.381</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.2759</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-0.256</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>-0.1208</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-0.073</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>33</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.9457</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.8447</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0.8562</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0.7313</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>34</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0.8149</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.7833</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0.6955</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>0.6878</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0.9049</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.7679</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0.7283</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>0.6903</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.6993</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>36</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0.5929</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.0209</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>0.1875</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>0.0179</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-0.3697</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>37</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0.8102</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.0216</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>0.4873</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>0.0802</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-0.3552</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>38</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0.6024</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.0042</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>0.7273</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0.3049</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>39</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0.7612</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.2252</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>0.7976</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>0.4027</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-0.1084</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>40</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0.7245</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.3198</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>0.6036</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>0.6176</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0.1626</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>41</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3964,8 +3964,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>30</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4012,25 +4014,15 @@
           <t>09-09_14-57-46_856_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞1.txt</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.82, Δ=-6.0% (147.91→139.006667); MDF↓ r=-0.75, Δ=-7.1% (127.736667→118.703333)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>MPF r=0.04, Δ=0.5%; MDF r=0.07, Δ=1.1%</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：否</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>31</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -4077,25 +4069,15 @@
           <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.46, Δ=-4.7% (148.453333→141.463333); MDF↓ r=-0.39, Δ=-5.5% (128.433333→121.376667)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>RMS↑ r=0.38, Δ=11.8% (0.13188→0.147459)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：弱／不明顯</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>32</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -4142,25 +4124,15 @@
           <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.48, Δ=-7.3% (138.84→128.65); MDF↓ r=-0.47, Δ=-9.3% (116.763333→105.92); RMS↑ r=0.67, Δ=26.3% (0.152492→0.192539); AEMG↑ r=0.69, Δ=25.2% (0.109463→0.137057)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.62, Δ=-7.9% (82.486667→75.946667); MDF↓ r=-0.68, Δ=-10.9% (75.926667→67.64); RMS↑ r=0.75, Δ=20.6% (0.138185→0.166663); AEMG↑ r=0.75, Δ=21.0% (0.105875→0.128127)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>33</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -4207,25 +4179,15 @@
           <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.91, Δ=-7.8% (146.676667→135.16); MDF↓ r=-0.93, Δ=-11.2% (127.44→113.206667)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.88, Δ=-6.1% (100.233333→94.093333); MDF↓ r=-0.76, Δ=-5.4% (93.796667→88.7)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>34</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -4272,25 +4234,15 @@
           <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.87, Δ=-7.2% (154.016667→142.976667); MDF↓ r=-0.82, Δ=-8.3% (132.22→121.273333)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.84, Δ=-5.2% (99.863333→94.636667); MDF↓ r=-0.75, Δ=-6.1% (94.106667→88.34)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>35</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4337,25 +4289,15 @@
           <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.86, Δ=-7.9% (159.316667→146.69); MDF↓ r=-0.80, Δ=-10.0% (137.976667→124.22)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.85, Δ=-5.2% (99.256667→94.043333); MDF↓ r=-0.82, Δ=-7.0% (94.053333→87.51)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>36</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4402,25 +4344,15 @@
           <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.55, Δ=-4.5% (109.433333→104.5); MDF↓ r=-0.46, Δ=-6.2% (86.54→81.143333)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.39, Δ=-16.4% (83.44→69.77); MDF↓ r=-0.39, Δ=-24.1% (75.236667→57.113333)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>37</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -4467,25 +4399,15 @@
           <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MDF↓ r=-0.53, Δ=-3.2% (92.536667→89.603333); RMS↑ r=0.64, Δ=22.7% (0.038883→0.047694); AEMG↑ r=0.64, Δ=21.9% (0.029716→0.03624)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>MPF r=-0.08, Δ=0.3%; MDF r=-0.20, Δ=-0.9%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：否</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>38</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4532,25 +4454,15 @@
           <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>MDF↓ r=-0.49, Δ=-3.3% (87.2→84.343333)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>MPF r=0.43, Δ=2.0%; MDF r=0.39, Δ=2.5%</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>綜合：弱／不明顯｜對照組：弱／不明顯｜實驗組：否</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>39</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4597,25 +4509,15 @@
           <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.61, Δ=-6.5% (102.746667→96.083333); MDF↓ r=-0.47, Δ=-5.2% (79.466667→75.373333); RMS↑ r=0.43, Δ=5.8% (0.046231→0.048923)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.45, Δ=-4.5% (69.413333→66.26); MDF↓ r=-0.52, Δ=-7.0% (62.256667→57.906667)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>40</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4662,25 +4564,15 @@
           <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.98, Δ=-16.6% (117.143333→97.633333); MDF↓ r=-0.94, Δ=-18.1% (90.883333→74.423333); RMS↑ r=0.85, Δ=37.2% (0.035401→0.048557); AEMG↑ r=0.87, Δ=33.9% (0.02664→0.035675)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.65, Δ=-16.3% (83.336667→69.766667); MDF↓ r=-0.63, Δ=-20.2% (78.303333→62.486667); RMS↑ r=0.83, Δ=25.8% (0.029084→0.036588); AEMG↑ r=0.77, Δ=27.1% (0.02443→0.031054)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：是</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>41</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4727,21 +4619,9 @@
           <t>09-09_14-42-34_881_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>MPF↓ r=-0.93, Δ=-10.3% (104.806667→94.016667); MDF↓ r=-0.86, Δ=-7.9% (80.363333→74.05); RMS↑ r=0.75, Δ=9.1% (0.042638→0.046512); AEMG↑ r=0.74, Δ=8.8% (0.031847→0.034638)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>RMS↑ r=0.39, Δ=6.9% (0.032725→0.034994)</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>綜合：是｜對照組：是｜實驗組：弱／不明顯</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5288,25 +5168,25 @@
         <v>0.454474</v>
       </c>
       <c r="M8" t="n">
-        <v>5.7578</v>
+        <v>5.2656</v>
       </c>
       <c r="N8" t="n">
-        <v>0.075778</v>
+        <v>0.06995999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.100535</v>
+        <v>0.09757</v>
       </c>
       <c r="P8" t="n">
-        <v>0.43439</v>
+        <v>0.367971</v>
       </c>
       <c r="Q8" t="n">
-        <v>115.28</v>
+        <v>137.02</v>
       </c>
       <c r="R8" t="n">
-        <v>105.08</v>
+        <v>126.61</v>
       </c>
       <c r="S8" t="n">
-        <v>0.185097</v>
+        <v>0.176702</v>
       </c>
     </row>
     <row r="9">
@@ -5353,25 +5233,25 @@
         <v>0.505972</v>
       </c>
       <c r="M9" t="n">
-        <v>6.9375</v>
+        <v>6.1436</v>
       </c>
       <c r="N9" t="n">
-        <v>0.083165</v>
+        <v>0.07903300000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.109775</v>
+        <v>0.109303</v>
       </c>
       <c r="P9" t="n">
-        <v>0.574247</v>
+        <v>0.48501</v>
       </c>
       <c r="Q9" t="n">
-        <v>101.92</v>
+        <v>126.7</v>
       </c>
       <c r="R9" t="n">
-        <v>87.81999999999999</v>
+        <v>112.47</v>
       </c>
       <c r="S9" t="n">
-        <v>0.237741</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="10">
@@ -5418,25 +5298,25 @@
         <v>0.505628</v>
       </c>
       <c r="M10" t="n">
-        <v>7.2812</v>
+        <v>6.9102</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0764</v>
+        <v>0.070142</v>
       </c>
       <c r="O10" t="n">
-        <v>0.102115</v>
+        <v>0.09805899999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.553906</v>
+        <v>0.484084</v>
       </c>
       <c r="Q10" t="n">
-        <v>104.04</v>
+        <v>122.54</v>
       </c>
       <c r="R10" t="n">
-        <v>88.34999999999999</v>
+        <v>106.27</v>
       </c>
       <c r="S10" t="n">
-        <v>0.230755</v>
+        <v>0.211974</v>
       </c>
     </row>
     <row r="11">
@@ -5483,25 +5363,25 @@
         <v>0.55974</v>
       </c>
       <c r="M11" t="n">
-        <v>6.1719</v>
+        <v>4.7324</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06821199999999999</v>
+        <v>0.069414</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08684699999999999</v>
+        <v>0.09474399999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4195</v>
+        <v>0.328268</v>
       </c>
       <c r="Q11" t="n">
-        <v>98.16</v>
+        <v>134.05</v>
       </c>
       <c r="R11" t="n">
-        <v>84.62</v>
+        <v>121.16</v>
       </c>
       <c r="S11" t="n">
-        <v>0.161222</v>
+        <v>0.151615</v>
       </c>
     </row>
     <row r="12">
@@ -5548,25 +5428,25 @@
         <v>0.60736</v>
       </c>
       <c r="M12" t="n">
-        <v>7.0723</v>
+        <v>5.8184</v>
       </c>
       <c r="N12" t="n">
-        <v>0.069628</v>
+        <v>0.07015299999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.091976</v>
+        <v>0.097095</v>
       </c>
       <c r="P12" t="n">
-        <v>0.492423</v>
+        <v>0.407293</v>
       </c>
       <c r="Q12" t="n">
-        <v>96.93000000000001</v>
+        <v>124.26</v>
       </c>
       <c r="R12" t="n">
-        <v>81.27</v>
+        <v>108.03</v>
       </c>
       <c r="S12" t="n">
-        <v>0.218956</v>
+        <v>0.216697</v>
       </c>
     </row>
     <row r="13">
@@ -5613,25 +5493,25 @@
         <v>0.490704</v>
       </c>
       <c r="M13" t="n">
-        <v>7.1338</v>
+        <v>6.0137</v>
       </c>
       <c r="N13" t="n">
-        <v>0.072548</v>
+        <v>0.07105499999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.096417</v>
+        <v>0.098576</v>
       </c>
       <c r="P13" t="n">
-        <v>0.517053</v>
+        <v>0.427031</v>
       </c>
       <c r="Q13" t="n">
-        <v>100.74</v>
+        <v>126.55</v>
       </c>
       <c r="R13" t="n">
-        <v>87.7</v>
+        <v>112.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0.204304</v>
+        <v>0.178432</v>
       </c>
     </row>
     <row r="14">
@@ -6458,25 +6338,25 @@
         <v>0.451181</v>
       </c>
       <c r="M26" t="n">
-        <v>7.1328</v>
+        <v>4.9844</v>
       </c>
       <c r="N26" t="n">
-        <v>0.298481</v>
+        <v>0.071842</v>
       </c>
       <c r="O26" t="n">
-        <v>0.313524</v>
+        <v>0.096565</v>
       </c>
       <c r="P26" t="n">
-        <v>2.115305</v>
+        <v>0.357759</v>
       </c>
       <c r="Q26" t="n">
-        <v>28.91</v>
+        <v>124.74</v>
       </c>
       <c r="R26" t="n">
-        <v>6.93</v>
+        <v>110.26</v>
       </c>
       <c r="S26" t="n">
-        <v>0.910978</v>
+        <v>0.158746</v>
       </c>
     </row>
     <row r="27">
@@ -6523,25 +6403,25 @@
         <v>0.516117</v>
       </c>
       <c r="M27" t="n">
-        <v>7.9375</v>
+        <v>5.8203</v>
       </c>
       <c r="N27" t="n">
-        <v>0.322332</v>
+        <v>0.066916</v>
       </c>
       <c r="O27" t="n">
-        <v>0.337824</v>
+        <v>0.091368</v>
       </c>
       <c r="P27" t="n">
-        <v>2.55851</v>
+        <v>0.387941</v>
       </c>
       <c r="Q27" t="n">
-        <v>23.13</v>
+        <v>117.29</v>
       </c>
       <c r="R27" t="n">
-        <v>8.82</v>
+        <v>104.56</v>
       </c>
       <c r="S27" t="n">
-        <v>1.290245</v>
+        <v>0.200599</v>
       </c>
     </row>
     <row r="28">
@@ -6588,25 +6468,25 @@
         <v>0.43352</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8437</v>
+        <v>5.6856</v>
       </c>
       <c r="N28" t="n">
-        <v>0.305821</v>
+        <v>0.07459300000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>0.323446</v>
+        <v>0.10171</v>
       </c>
       <c r="P28" t="n">
-        <v>2.394518</v>
+        <v>0.422579</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.12</v>
+        <v>118.67</v>
       </c>
       <c r="R28" t="n">
-        <v>8.380000000000001</v>
+        <v>107.74</v>
       </c>
       <c r="S28" t="n">
-        <v>1.480354</v>
+        <v>0.176343</v>
       </c>
     </row>
     <row r="29">
@@ -6653,25 +6533,25 @@
         <v>0.40878</v>
       </c>
       <c r="M29" t="n">
-        <v>6.8594</v>
+        <v>5.3594</v>
       </c>
       <c r="N29" t="n">
-        <v>0.112562</v>
+        <v>0.064979</v>
       </c>
       <c r="O29" t="n">
-        <v>0.13135</v>
+        <v>0.087433</v>
       </c>
       <c r="P29" t="n">
-        <v>0.770598</v>
+        <v>0.347887</v>
       </c>
       <c r="Q29" t="n">
-        <v>57.84</v>
+        <v>120.14</v>
       </c>
       <c r="R29" t="n">
-        <v>34.89</v>
+        <v>107.44</v>
       </c>
       <c r="S29" t="n">
-        <v>0.435293</v>
+        <v>0.185462</v>
       </c>
     </row>
     <row r="30">
@@ -6718,25 +6598,25 @@
         <v>0.42312</v>
       </c>
       <c r="M30" t="n">
-        <v>6.6484</v>
+        <v>5.3359</v>
       </c>
       <c r="N30" t="n">
-        <v>0.114025</v>
+        <v>0.07448200000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>0.135867</v>
+        <v>0.101889</v>
       </c>
       <c r="P30" t="n">
-        <v>0.7534149999999999</v>
+        <v>0.397401</v>
       </c>
       <c r="Q30" t="n">
-        <v>67.3</v>
+        <v>122.37</v>
       </c>
       <c r="R30" t="n">
-        <v>50.79</v>
+        <v>108.42</v>
       </c>
       <c r="S30" t="n">
-        <v>0.396659</v>
+        <v>0.182176</v>
       </c>
     </row>
     <row r="31">
@@ -6783,25 +6663,25 @@
         <v>0.428612</v>
       </c>
       <c r="M31" t="n">
-        <v>7.0547</v>
+        <v>5.6797</v>
       </c>
       <c r="N31" t="n">
-        <v>0.086494</v>
+        <v>0.06525</v>
       </c>
       <c r="O31" t="n">
-        <v>0.105908</v>
+        <v>0.08802500000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>0.6064349999999999</v>
+        <v>0.368512</v>
       </c>
       <c r="Q31" t="n">
-        <v>74.06</v>
+        <v>120.84</v>
       </c>
       <c r="R31" t="n">
-        <v>61.01</v>
+        <v>107.39</v>
       </c>
       <c r="S31" t="n">
-        <v>0.260446</v>
+        <v>0.195902</v>
       </c>
     </row>
     <row r="32">
@@ -7433,25 +7313,25 @@
         <v>0.092262</v>
       </c>
       <c r="M41" t="n">
-        <v>7.4375</v>
+        <v>5.2266</v>
       </c>
       <c r="N41" t="n">
-        <v>0.09046</v>
+        <v>0.01858</v>
       </c>
       <c r="O41" t="n">
-        <v>0.09494900000000001</v>
+        <v>0.023931</v>
       </c>
       <c r="P41" t="n">
-        <v>0.647571</v>
+        <v>0.096834</v>
       </c>
       <c r="Q41" t="n">
-        <v>30.87</v>
+        <v>118.72</v>
       </c>
       <c r="R41" t="n">
-        <v>8</v>
+        <v>99.09</v>
       </c>
       <c r="S41" t="n">
-        <v>0.282637</v>
+        <v>0.039551</v>
       </c>
     </row>
     <row r="42">
@@ -7498,25 +7378,25 @@
         <v>0.113258</v>
       </c>
       <c r="M42" t="n">
-        <v>9.1875</v>
+        <v>5.1015</v>
       </c>
       <c r="N42" t="n">
-        <v>0.088337</v>
+        <v>0.02167</v>
       </c>
       <c r="O42" t="n">
-        <v>0.094504</v>
+        <v>0.028305</v>
       </c>
       <c r="P42" t="n">
-        <v>0.81023</v>
+        <v>0.11041</v>
       </c>
       <c r="Q42" t="n">
-        <v>27.69</v>
+        <v>119.5</v>
       </c>
       <c r="R42" t="n">
-        <v>8.390000000000001</v>
+        <v>104.02</v>
       </c>
       <c r="S42" t="n">
-        <v>0.301553</v>
+        <v>0.044486</v>
       </c>
     </row>
     <row r="43">
@@ -7563,25 +7443,25 @@
         <v>0.09807100000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8281</v>
+        <v>5.6172</v>
       </c>
       <c r="N43" t="n">
-        <v>0.150799</v>
+        <v>0.022127</v>
       </c>
       <c r="O43" t="n">
-        <v>0.156503</v>
+        <v>0.028681</v>
       </c>
       <c r="P43" t="n">
-        <v>0.572532</v>
+        <v>0.123779</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.54</v>
+        <v>113.39</v>
       </c>
       <c r="R43" t="n">
-        <v>0.66</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="S43" t="n">
-        <v>0.349379</v>
+        <v>0.043558</v>
       </c>
     </row>
     <row r="44">
@@ -7628,25 +7508,25 @@
         <v>0.092568</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2812</v>
+        <v>5.4609</v>
       </c>
       <c r="N44" t="n">
-        <v>0.179489</v>
+        <v>0.019347</v>
       </c>
       <c r="O44" t="n">
-        <v>0.188199</v>
+        <v>0.024897</v>
       </c>
       <c r="P44" t="n">
-        <v>0.577488</v>
+        <v>0.105615</v>
       </c>
       <c r="Q44" t="n">
-        <v>16.98</v>
+        <v>108.58</v>
       </c>
       <c r="R44" t="n">
-        <v>5.27</v>
+        <v>88.14</v>
       </c>
       <c r="S44" t="n">
-        <v>0.55576</v>
+        <v>0.035493</v>
       </c>
     </row>
     <row r="45">
@@ -7693,25 +7573,25 @@
         <v>0.08230800000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>2.125</v>
+        <v>5.8828</v>
       </c>
       <c r="N45" t="n">
-        <v>0.243933</v>
+        <v>0.020675</v>
       </c>
       <c r="O45" t="n">
-        <v>0.252985</v>
+        <v>0.026677</v>
       </c>
       <c r="P45" t="n">
-        <v>0.514948</v>
+        <v>0.121252</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.46</v>
+        <v>105.15</v>
       </c>
       <c r="R45" t="n">
-        <v>0.49</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>0.510692</v>
+        <v>0.042627</v>
       </c>
     </row>
     <row r="46">
@@ -7758,25 +7638,25 @@
         <v>0.100703</v>
       </c>
       <c r="M46" t="n">
-        <v>2.6875</v>
+        <v>5.9376</v>
       </c>
       <c r="N46" t="n">
-        <v>0.1767</v>
+        <v>0.021276</v>
       </c>
       <c r="O46" t="n">
-        <v>0.189297</v>
+        <v>0.027674</v>
       </c>
       <c r="P46" t="n">
-        <v>0.463235</v>
+        <v>0.125586</v>
       </c>
       <c r="Q46" t="n">
-        <v>12.04</v>
+        <v>102.96</v>
       </c>
       <c r="R46" t="n">
-        <v>3.65</v>
+        <v>84.19</v>
       </c>
       <c r="S46" t="n">
-        <v>0.5703009999999999</v>
+        <v>0.044924</v>
       </c>
     </row>
     <row r="47">
@@ -8603,25 +8483,25 @@
         <v>0.040262</v>
       </c>
       <c r="M59" t="n">
-        <v>2.6484</v>
+        <v>5.1406</v>
       </c>
       <c r="N59" t="n">
-        <v>0.056671</v>
+        <v>0.012837</v>
       </c>
       <c r="O59" t="n">
-        <v>0.05902</v>
+        <v>0.016508</v>
       </c>
       <c r="P59" t="n">
-        <v>0.146905</v>
+        <v>0.065535</v>
       </c>
       <c r="Q59" t="n">
-        <v>7.66</v>
+        <v>102.06</v>
       </c>
       <c r="R59" t="n">
-        <v>1.54</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="S59" t="n">
-        <v>0.118041</v>
+        <v>0.021711</v>
       </c>
     </row>
     <row r="60">
@@ -8668,25 +8548,25 @@
         <v>0.049486</v>
       </c>
       <c r="M60" t="n">
-        <v>7.6328</v>
+        <v>5.8282</v>
       </c>
       <c r="N60" t="n">
-        <v>0.065194</v>
+        <v>0.013685</v>
       </c>
       <c r="O60" t="n">
-        <v>0.068802</v>
+        <v>0.017725</v>
       </c>
       <c r="P60" t="n">
-        <v>0.491369</v>
+        <v>0.079036</v>
       </c>
       <c r="Q60" t="n">
-        <v>27.85</v>
+        <v>106.54</v>
       </c>
       <c r="R60" t="n">
-        <v>5.7</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="S60" t="n">
-        <v>0.274549</v>
+        <v>0.026157</v>
       </c>
     </row>
     <row r="61">
@@ -8732,27 +8612,6 @@
       <c r="L61" t="n">
         <v>0.060815</v>
       </c>
-      <c r="M61" t="n">
-        <v>9.148400000000001</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.081832</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.08520800000000001</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0.737121</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="R61" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.372103</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8798,25 +8657,25 @@
         <v>0.031947</v>
       </c>
       <c r="M62" t="n">
-        <v>2.7813</v>
+        <v>4.914</v>
       </c>
       <c r="N62" t="n">
-        <v>0.06828099999999999</v>
+        <v>0.012599</v>
       </c>
       <c r="O62" t="n">
-        <v>0.071342</v>
+        <v>0.016218</v>
       </c>
       <c r="P62" t="n">
-        <v>0.186575</v>
+        <v>0.06134</v>
       </c>
       <c r="Q62" t="n">
-        <v>7.22</v>
+        <v>111.39</v>
       </c>
       <c r="R62" t="n">
-        <v>1.83</v>
+        <v>80.94</v>
       </c>
       <c r="S62" t="n">
-        <v>0.168204</v>
+        <v>0.021651</v>
       </c>
     </row>
     <row r="63">
@@ -8863,25 +8722,25 @@
         <v>0.04502</v>
       </c>
       <c r="M63" t="n">
-        <v>7.7109</v>
+        <v>5.2344</v>
       </c>
       <c r="N63" t="n">
-        <v>0.077921</v>
+        <v>0.012892</v>
       </c>
       <c r="O63" t="n">
-        <v>0.081286</v>
+        <v>0.01661</v>
       </c>
       <c r="P63" t="n">
-        <v>0.599059</v>
+        <v>0.06737899999999999</v>
       </c>
       <c r="Q63" t="n">
-        <v>22.88</v>
+        <v>109.38</v>
       </c>
       <c r="R63" t="n">
-        <v>3.84</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="S63" t="n">
-        <v>0.293972</v>
+        <v>0.022396</v>
       </c>
     </row>
     <row r="64">
@@ -8926,27 +8785,6 @@
       </c>
       <c r="L64" t="n">
         <v>0.049898</v>
-      </c>
-      <c r="M64" t="n">
-        <v>7.836</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0.070884</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0.07475900000000001</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0.553886</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="R64" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0.241244</v>
       </c>
     </row>
     <row r="65">
@@ -18479,10 +18317,10 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6551</v>
+        <v>0.8317</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6945</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="17">
@@ -18513,10 +18351,10 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6987</v>
+        <v>0.7393</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0097</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="18">
@@ -18547,10 +18385,10 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8007</v>
+        <v>0.8706</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0174</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="19">
@@ -18581,10 +18419,10 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5505</v>
+        <v>0.6493</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0058</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="20">
@@ -18615,10 +18453,10 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.9777</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7088</v>
+        <v>0.1926</v>
       </c>
     </row>
     <row r="21">
@@ -18649,10 +18487,10 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8367</v>
+        <v>0.989</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0983</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="22">
@@ -18683,10 +18521,10 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9932</v>
+        <v>0.945</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0224</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="23">
@@ -18717,10 +18555,10 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5137</v>
+        <v>0.5845</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="24">
@@ -18751,10 +18589,10 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7741</v>
+        <v>-0.855</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0052</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="25">
@@ -18785,10 +18623,10 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8567</v>
+        <v>-0.8839</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0262</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="26">
@@ -18819,10 +18657,10 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8963</v>
+        <v>-0.9321</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0039</v>
       </c>
     </row>
     <row r="27">
@@ -18853,10 +18691,10 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0673</v>
+        <v>0.9525</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0123</v>
+        <v>0.2347</v>
       </c>
     </row>
     <row r="28">
@@ -18887,10 +18725,10 @@
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0358</v>
+        <v>0.9982</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0008</v>
+        <v>0.6076</v>
       </c>
     </row>
     <row r="29">
@@ -18921,10 +18759,10 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1405</v>
+        <v>0.4962</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0038</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="30">
@@ -19907,10 +19745,10 @@
         <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.9046</v>
+        <v>-0.8851</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0192</v>
+        <v>-0.8167</v>
       </c>
     </row>
     <row r="59">
@@ -19941,10 +19779,10 @@
         <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.9984</v>
+        <v>0.8196</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.0086</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="60">
@@ -19975,10 +19813,10 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.9978</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0106</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="61">
@@ -20009,10 +19847,10 @@
         <v>3</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.9597</v>
+        <v>0.7936</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0265</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="62">
@@ -20043,10 +19881,10 @@
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.9127999999999999</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0007</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="63">
@@ -20077,10 +19915,10 @@
         <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0024</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="64">
@@ -20111,10 +19949,10 @@
         <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.0149</v>
+        <v>0.8042</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="65">
@@ -20145,10 +19983,10 @@
         <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7786</v>
+        <v>0.9813</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0462</v>
+        <v>0.9241</v>
       </c>
     </row>
     <row r="66">
@@ -20179,10 +20017,10 @@
         <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4044</v>
+        <v>0.9916</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0244</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -20213,10 +20051,10 @@
         <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.6747</v>
+        <v>0.7377</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1626</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="68">
@@ -20247,10 +20085,10 @@
         <v>3</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1823</v>
+        <v>0.9029</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0059</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -20281,10 +20119,10 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.8043</v>
+        <v>0.5266</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.0638</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="70">
@@ -20315,10 +20153,10 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.9496</v>
+        <v>-0.0888</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.0573</v>
+        <v>-0.0007</v>
       </c>
     </row>
     <row r="71">
@@ -20349,10 +20187,10 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.8452</v>
+        <v>0.5344</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.1915</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="72">
@@ -21097,10 +20935,10 @@
         <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.9998</v>
+        <v>0.994</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.2924</v>
+        <v>0.1904</v>
       </c>
     </row>
     <row r="94">
@@ -21131,10 +20969,10 @@
         <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3025</v>
+        <v>0.9538</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0054</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="95">
@@ -21165,10 +21003,10 @@
         <v>3</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.3862</v>
+        <v>0.9962</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.0062</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="96">
@@ -21199,10 +21037,10 @@
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4625</v>
+        <v>0.9942</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0136</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="97">
@@ -21233,10 +21071,10 @@
         <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9294</v>
+        <v>0.9789</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0017</v>
+        <v>0.2387</v>
       </c>
     </row>
     <row r="98">
@@ -21267,10 +21105,10 @@
         <v>3</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.8903</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0037</v>
+        <v>0.0722</v>
       </c>
     </row>
     <row r="99">
@@ -21301,10 +21139,10 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0262</v>
+        <v>0.8264</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0004</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="100">
@@ -21335,10 +21173,10 @@
         <v>3</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.7663</v>
+        <v>0.9964</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.0067</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="101">
@@ -21369,10 +21207,10 @@
         <v>3</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.5966</v>
+        <v>-0.8953</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0034</v>
       </c>
     </row>
     <row r="102">
@@ -21403,10 +21241,10 @@
         <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.8292</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.0018</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="103">
@@ -21437,10 +21275,10 @@
         <v>3</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.576</v>
+        <v>-0.9056999999999999</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.0004</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="104">
@@ -21471,10 +21309,10 @@
         <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.0518</v>
+        <v>0.9293</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.0001</v>
+        <v>0.1366</v>
       </c>
     </row>
     <row r="105">
@@ -21505,10 +21343,10 @@
         <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1999</v>
+        <v>0.9569</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0008</v>
+        <v>0.1245</v>
       </c>
     </row>
     <row r="106">
@@ -21539,10 +21377,10 @@
         <v>3</v>
       </c>
       <c r="G106" t="n">
-        <v>0.9757</v>
+        <v>0.1683</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0027</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="107">
@@ -22522,13 +22360,13 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.1153</v>
+        <v>-1</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.0133</v>
+        <v>-0.2095</v>
       </c>
     </row>
     <row r="136">
@@ -22556,13 +22394,13 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>0.9596</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0.0623</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="137">
@@ -22590,13 +22428,13 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>0.9939</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1219</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="138">
@@ -22624,13 +22462,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9681999999999999</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.0973</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="139">
@@ -22658,13 +22496,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.1702</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.0001</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="140">
@@ -22692,13 +22530,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.2509</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.0012</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="141">
@@ -22726,13 +22564,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
-        <v>0.9816</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0.0482</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -22760,13 +22598,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.8501</v>
+        <v>-1</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.4836</v>
+        <v>-0.2376</v>
       </c>
     </row>
     <row r="143">
@@ -22794,13 +22632,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G143" t="n">
-        <v>0.6166</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0125</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="144">
@@ -22828,13 +22666,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>0.8457</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0696</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="145">
@@ -22862,13 +22700,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
-        <v>0.6576</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>0.0201</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="146">
@@ -22896,13 +22734,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.9167999999999999</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.0022</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="147">
@@ -22930,13 +22768,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.4564</v>
+        <v>-1</v>
       </c>
       <c r="H147" t="n">
-        <v>-0.0037</v>
+        <v>-0.1467</v>
       </c>
     </row>
     <row r="148">
@@ -22964,13 +22802,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G148" t="n">
-        <v>0.7671</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0225</v>
+        <v>0.0306</v>
       </c>
     </row>
     <row r="149">

--- a/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
+++ b/data/pairing_results/2609-21_ZE1_list/analysis_results.xlsx
@@ -507,10 +507,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -532,10 +530,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F2" t="n">
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -552,30 +548,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.6936</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.0953</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.8403</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.0459</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6447</t>
-        </is>
+      <c r="J2" t="n">
+        <v>0.9597</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9984</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6447000000000001</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -594,10 +580,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A3" t="n">
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -619,10 +603,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F3" t="n">
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -639,30 +621,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.9523</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.4956</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.9155</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.1797</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-0.1614</t>
-        </is>
+      <c r="J3" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1614</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -681,10 +653,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A4" t="n">
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -706,10 +676,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F4" t="n">
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -727,16 +695,16 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6493</v>
+        <v>0.8285</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0089</v>
+        <v>0.0102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8706</v>
+        <v>0.8647</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0135</v>
+        <v>0.0053</v>
       </c>
       <c r="N4" t="n">
         <v>0.5121</v>
@@ -758,10 +726,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A5" t="n">
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -783,10 +749,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F5" t="n">
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -804,16 +768,16 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.9321</v>
+        <v>0.9764</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0039</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8839</v>
+        <v>0.9848</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0205</v>
+        <v>0.0108</v>
       </c>
       <c r="N5" t="n">
         <v>0.7771</v>
@@ -835,10 +799,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A6" t="n">
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -860,10 +822,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F6" t="n">
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -880,30 +840,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-0.4749</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-0.5168</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-0.7684</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-0.4574</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-0.499</t>
-        </is>
+      <c r="J6" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.499</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -922,10 +872,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A7" t="n">
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -947,10 +895,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F7" t="n">
+        <v>3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -967,30 +913,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-0.7006</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-0.072</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-0.9182</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>-2.0894</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.7207</t>
-        </is>
+      <c r="J7" t="n">
+        <v>-0.5216</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9842</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7207</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1009,10 +945,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A8" t="n">
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1034,10 +968,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F8" t="n">
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1054,30 +986,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-0.4897</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-0.0552</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-0.104</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>-0.0058</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.5556</t>
-        </is>
+      <c r="J8" t="n">
+        <v>0.7672</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4969</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1096,10 +1018,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A9" t="n">
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1121,10 +1041,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1141,30 +1059,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.0406</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-0.9059</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>-0.0365</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.464</t>
-        </is>
+      <c r="J9" t="n">
+        <v>0.6876</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.464</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1183,10 +1091,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A10" t="n">
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1208,10 +1114,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F10" t="n">
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1229,16 +1133,16 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.7936</v>
+        <v>0.9905</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0028</v>
+        <v>0.0053</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.9233</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.005</v>
+        <v>0.0064</v>
       </c>
       <c r="N10" t="n">
         <v>0.5620000000000001</v>
@@ -1260,10 +1164,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A11" t="n">
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1285,10 +1187,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F11" t="n">
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1337,10 +1237,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A12" t="n">
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1362,10 +1260,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F12" t="n">
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1382,30 +1278,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.3934</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.0502</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0.9941</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0.5656</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.6124</t>
-        </is>
+      <c r="J12" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9941</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5656</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6124000000000001</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1424,10 +1310,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A13" t="n">
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1449,10 +1333,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F13" t="n">
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1469,30 +1351,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.5961</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.1069</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0.8331</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.4926</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.3345</t>
-        </is>
+      <c r="J13" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3345</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1511,10 +1383,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A14" t="n">
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1536,10 +1406,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F14" t="n">
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1556,30 +1424,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-0.9834</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-0.1645</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0.8464</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>0.6329</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-0.474</t>
-        </is>
+      <c r="J14" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1343</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.5484</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1598,10 +1456,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A15" t="n">
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1623,10 +1479,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F15" t="n">
+        <v>3</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -1661,10 +1515,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A16" t="n">
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1686,10 +1538,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F16" t="n">
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1707,16 +1557,16 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.9942</v>
+        <v>0.9938</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0263</v>
+        <v>0.0252</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9962</v>
+        <v>0.9999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0291</v>
+        <v>0.0264</v>
       </c>
       <c r="N16" t="n">
         <v>0.6551</v>
@@ -1738,10 +1588,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A17" t="n">
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1763,10 +1611,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F17" t="n">
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1784,16 +1630,16 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.9161</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7597</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0032</v>
+        <v>0.0024</v>
       </c>
       <c r="N17" t="n">
         <v>0.6901</v>
@@ -1815,10 +1661,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A18" t="n">
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1840,10 +1684,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F18" t="n">
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1860,30 +1702,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-0.3058</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-0.0444</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.6406</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>0.0136</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-0.6372</t>
-        </is>
+      <c r="J18" t="n">
+        <v>-0.3579</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.7328</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.6372</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1902,10 +1734,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A19" t="n">
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1927,10 +1757,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F19" t="n">
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1947,30 +1775,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.9522</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.1667</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>0.9393</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>0.0816</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0.7142</t>
-        </is>
+      <c r="J19" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.7141999999999999</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1989,10 +1807,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2014,10 +1830,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F20" t="n">
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2034,30 +1848,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-0.7192</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-1.3328</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-0.9813</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-1.1669</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-0.1774</t>
-        </is>
+      <c r="J20" t="n">
+        <v>0.9238</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.6686</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8474</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.2576</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2076,10 +1880,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A21" t="n">
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2101,10 +1903,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2121,30 +1921,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>-0.9122</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-0.0962</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.9942</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>0.6884</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.2577</t>
-        </is>
+      <c r="J21" t="n">
+        <v>-0.9997</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.8322</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.7843</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2577</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2163,10 +1953,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A22" t="n">
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2188,10 +1976,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F22" t="n">
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2240,10 +2026,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A23" t="n">
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2265,10 +2049,8 @@
           <t>a10</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F23" t="n">
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2317,10 +2099,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A24" t="n">
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2342,10 +2122,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F24" t="n">
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2362,30 +2140,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0.9654</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.6655</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>0.9904</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>0.8479</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0.4885</t>
-        </is>
+      <c r="J24" t="n">
+        <v>0.9699</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.6992</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.9711</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.4885</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2404,10 +2172,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A25" t="n">
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2429,10 +2195,8 @@
           <t>ze2</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F25" t="n">
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2449,30 +2213,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0.6147</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.3277</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>0.3241</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>0.1419</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-0.5826</t>
-        </is>
+      <c r="J25" t="n">
+        <v>0.9219000000000001</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9427</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4923</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.5826</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2491,10 +2245,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A26" t="n">
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2516,10 +2268,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F26" t="n">
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2536,30 +2286,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>-0.996</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>-0.3202</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-0.9545</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>-1.0625</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0.6523</t>
-        </is>
+      <c r="J26" t="n">
+        <v>-0.4491</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.1963</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.9001</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.6704</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2578,10 +2318,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A27" t="n">
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2603,10 +2341,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F27" t="n">
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2623,30 +2359,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.9191</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.1011</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.9768</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>0.4132</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-0.525</t>
-        </is>
+      <c r="J27" t="n">
+        <v>-0.4373</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.8863</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.0198</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.4959</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2665,10 +2391,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A28" t="n">
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2690,10 +2414,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F28" t="n">
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2710,30 +2432,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>-0.9381</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>-0.0371</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.9944</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>0.0756</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0.5324</t>
-        </is>
+      <c r="J28" t="n">
+        <v>-0.9968</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.9658</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.5355</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2752,10 +2464,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A29" t="n">
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2777,10 +2487,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="F29" t="n">
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2797,30 +2505,20 @@
           <t>3/3</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0.028</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.035</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>-0.9979</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>-0.4554</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0.1333</t>
-        </is>
+      <c r="J29" t="n">
+        <v>-0.9712</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.8993</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.7612</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.3477</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.1567</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2839,10 +2537,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A30" t="n">
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2864,10 +2560,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F30" t="n">
+        <v>10</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2884,30 +2578,20 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0.3741</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.0834</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>0.2904</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>0.1762</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-0.2449</t>
-        </is>
+      <c r="J30" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.2449</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2926,10 +2610,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A31" t="n">
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2951,10 +2633,8 @@
           <t>a09</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="F31" t="n">
+        <v>10</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2971,914 +2651,764 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0.8488</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.3082</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>-0.7219</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>-0.4582</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-0.3006</t>
-        </is>
+      <c r="J31" t="n">
+        <v>0.8938</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-0.7912</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.5775</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-0.2501</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>32</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1119</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.0565</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>33</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9477</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.7313</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>34</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8647</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.8401999999999999</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9177</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8036</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.9396</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.6993</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>36</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-0.3697</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>37</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-0.3087</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>38</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>疲勞</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7060999999999999</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>弱／不明顯</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>39</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>疲勞</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0.381</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.2759</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-0.256</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>-0.1208</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-0.073</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
+      <c r="J39" t="n">
+        <v>0.7714</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.8007</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-0.1084</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="n">
+        <v>40</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>疲勞</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.9457</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.8447</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0.8562</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0.7313</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
+      <c r="J40" t="n">
+        <v>0.7974</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.6532</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="n">
+        <v>41</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>疲勞</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>09-09_14-42-34_881_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0.8149</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.7833</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0.6955</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>0.6878</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
+      <c r="J41" t="n">
+        <v>0.4553</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0.9049</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.7679</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0.7283</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>0.6903</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.6993</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0.5929</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.0209</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>0.1875</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>0.0179</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-0.3697</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0.8102</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.0216</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>0.4873</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>0.0802</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>-0.3552</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0.6024</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.0042</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>0.7273</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0.3049</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0.7612</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.2252</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>0.7976</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>0.4027</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-0.1084</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0.7245</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.3198</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>0.6036</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>0.6176</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>0.1626</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>疲勞</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>09-09_14-42-34_881_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0.5415</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.0727</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>0.3837</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>0.324</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-0.107</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
         </is>
       </c>
     </row>
@@ -3964,10 +3494,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A2" t="n">
+        <v>30</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -4014,15 +3542,25 @@
           <t>09-09_14-57-46_856_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞1.txt</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.82, Δ=-6.0% (147.91→139.006667); MDF↓ r=-0.75, Δ=-7.1% (127.736667→118.703333)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MPF r=-0.07, Δ=-0.5%; MDF r=-0.05, Δ=-0.6%</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：否</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A3" t="n">
+        <v>31</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -4046,569 +3584,669 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MPF r=-0.33, Δ=-3.8%; MDF r=-0.29, Δ=-4.5%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>RMS↑ r=0.38, Δ=11.8% (0.13188→0.147459)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>綜合：弱／不明顯｜對照組：否｜實驗組：弱／不明顯</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>右脛前肌</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.48, Δ=-7.3% (138.84→128.65); MDF↓ r=-0.47, Δ=-9.3% (116.763333→105.92); RMS↑ r=0.67, Δ=26.3% (0.152492→0.192539); AEMG↑ r=0.69, Δ=25.2% (0.109463→0.137057)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.64, Δ=-8.2% (82.766667→75.946667); MDF↓ r=-0.70, Δ=-11.4% (76.363333→67.64); RMS↑ r=0.78, Δ=17.7% (0.141615→0.166663); AEMG↑ r=0.78, Δ=18.2% (0.108411→0.128127)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.91, Δ=-7.8% (146.676667→135.16); MDF↓ r=-0.93, Δ=-11.2% (127.44→113.206667)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.87, Δ=-5.8% (99.856667→94.093333); MDF↓ r=-0.76, Δ=-5.3% (93.633333→88.7)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.87, Δ=-7.2% (154.016667→142.976667); MDF↓ r=-0.82, Δ=-8.3% (132.22→121.273333)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.85, Δ=-4.8% (99.37→94.636667); MDF↓ r=-0.76, Δ=-5.6% (93.573333→88.34)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>左脛前肌</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.86, Δ=-7.9% (159.316667→146.69); MDF↓ r=-0.80, Δ=-10.0% (137.976667→124.22)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.86, Δ=-4.5% (98.526667→94.043333); MDF↓ r=-0.82, Δ=-5.8% (92.926667→87.51)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.55, Δ=-4.5% (109.433333→104.5); MDF↓ r=-0.46, Δ=-6.2% (86.54→81.143333)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.39, Δ=-16.4% (83.44→69.77); MDF↓ r=-0.39, Δ=-24.1% (75.236667→57.113333)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MDF↓ r=-0.68, Δ=-4.1% (93.463333→89.603333); RMS↑ r=0.64, Δ=21.5% (0.039252→0.047694); AEMG↑ r=0.64, Δ=21.0% (0.02996→0.03624)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MPF r=-0.03, Δ=0.6%; MDF r=-0.17, Δ=-0.7%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>右腓腸肌</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>弱／不明顯</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>09-09_15-01-03_995_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>弱／不明顯</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MDF↓ r=-0.49, Δ=-3.3% (87.2→84.343333)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MPF r=0.71, Δ=3.1%; MDF r=0.61, Δ=4.3%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>綜合：弱／不明顯｜對照組：弱／不明顯｜實驗組：否</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>右脛前肌</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>09-09_15-05-27_867_ExgCh1Data_(Frank 右脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.61, Δ=-6.5% (102.746667→96.083333); MDF↓ r=-0.47, Δ=-5.2% (79.466667→75.373333); RMS↑ r=0.43, Δ=5.8% (0.046231→0.048923)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.41, Δ=-3.3% (68.523333→66.26); MDF↓ r=-0.49, Δ=-5.3% (61.153333→57.906667)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>09-09_12-42-56_134_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.98, Δ=-16.6% (117.143333→97.633333); MDF↓ r=-0.94, Δ=-18.1% (90.883333→74.423333); RMS↑ r=0.85, Δ=37.2% (0.035401→0.048557); AEMG↑ r=0.87, Δ=33.9% (0.02664→0.035675)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.67, Δ=-13.8% (80.923333→69.766667); MDF↓ r=-0.65, Δ=-16.8% (75.11→62.486667); RMS↑ r=0.87, Δ=19.8% (0.030545→0.036588); AEMG↑ r=0.82, Δ=19.8% (0.025925→0.031054)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：是</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>左腓腸肌</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>a09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>09-09_12-47-55_198_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>左脛前肌</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左脛前肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>09-09_12-51-53_172_ExgCh2Data_(Frank 左脛前肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>09-09_15-20-08_195_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>09-09_15-23-04_934_ExgCh2Data_(Frank 右腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>右腓腸肌</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2609-09 frank 右腓腸肌_a09_褲XL_疲勞3.csv</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>09-09_15-25-56_272_ExgCh2Data(Frank 右腓腸肌)_a09_褲XL_疲勞3.txt</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞1.csv</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>09-09_14-34-47_174_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞1.txt</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞2.csv</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>09-09_14-38-43_403_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞2.txt</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>左腓腸肌</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>a09</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>弱／不明顯</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>2609-09 frank 左腓腸肌_a09_褲XL_疲勞3.csv</t>
@@ -4619,9 +4257,21 @@
           <t>09-09_14-42-34_881_ExgCh1Data_(Frank 左腓腸肌)_a09_褲XL_疲勞3.txt</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MPF↓ r=-0.93, Δ=-10.3% (104.806667→94.016667); MDF↓ r=-0.86, Δ=-7.9% (80.363333→74.05); RMS↑ r=0.75, Δ=9.1% (0.042638→0.046512); AEMG↑ r=0.74, Δ=8.8% (0.031847→0.034638)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MPF r=0.15, Δ=1.6%; MDF r=0.14, Δ=1.1%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>綜合：是｜對照組：是｜實驗組：否</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4778,25 +4428,25 @@
         <v>0.608909</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2637</v>
+        <v>6.2246</v>
       </c>
       <c r="N2" t="n">
-        <v>0.142313</v>
+        <v>0.147727</v>
       </c>
       <c r="O2" t="n">
-        <v>0.188922</v>
+        <v>0.200645</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7485309999999999</v>
+        <v>0.919345</v>
       </c>
       <c r="Q2" t="n">
-        <v>112.19</v>
+        <v>109.9</v>
       </c>
       <c r="R2" t="n">
-        <v>108.75</v>
+        <v>106.03</v>
       </c>
       <c r="S2" t="n">
-        <v>0.315783</v>
+        <v>0.399139</v>
       </c>
     </row>
     <row r="3">
@@ -4973,25 +4623,25 @@
         <v>0.482655</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0596</v>
+        <v>5.1348</v>
       </c>
       <c r="N5" t="n">
-        <v>0.128453</v>
+        <v>0.143749</v>
       </c>
       <c r="O5" t="n">
-        <v>0.173646</v>
+        <v>0.194308</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5207079999999999</v>
+        <v>0.737112</v>
       </c>
       <c r="Q5" t="n">
-        <v>112.53</v>
+        <v>110.01</v>
       </c>
       <c r="R5" t="n">
-        <v>108.98</v>
+        <v>105.9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.292182</v>
+        <v>0.449001</v>
       </c>
     </row>
     <row r="6">
@@ -5168,25 +4818,25 @@
         <v>0.454474</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2656</v>
+        <v>6.0937</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06995999999999999</v>
+        <v>0.072507</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09757</v>
+        <v>0.100768</v>
       </c>
       <c r="P8" t="n">
-        <v>0.367971</v>
+        <v>0.441777</v>
       </c>
       <c r="Q8" t="n">
-        <v>137.02</v>
+        <v>132.45</v>
       </c>
       <c r="R8" t="n">
-        <v>126.61</v>
+        <v>120.94</v>
       </c>
       <c r="S8" t="n">
-        <v>0.176702</v>
+        <v>0.204313</v>
       </c>
     </row>
     <row r="9">
@@ -5363,25 +5013,25 @@
         <v>0.55974</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7324</v>
+        <v>5.8574</v>
       </c>
       <c r="N11" t="n">
-        <v>0.069414</v>
+        <v>0.07699400000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09474399999999999</v>
+        <v>0.104323</v>
       </c>
       <c r="P11" t="n">
-        <v>0.328268</v>
+        <v>0.450718</v>
       </c>
       <c r="Q11" t="n">
-        <v>134.05</v>
+        <v>130.61</v>
       </c>
       <c r="R11" t="n">
-        <v>121.16</v>
+        <v>117</v>
       </c>
       <c r="S11" t="n">
-        <v>0.151615</v>
+        <v>0.23056</v>
       </c>
     </row>
     <row r="12">
@@ -5558,25 +5208,25 @@
         <v>0.478156</v>
       </c>
       <c r="M14" t="n">
-        <v>2.624</v>
+        <v>5.008</v>
       </c>
       <c r="N14" t="n">
-        <v>0.162133</v>
+        <v>0.20749</v>
       </c>
       <c r="O14" t="n">
-        <v>0.224784</v>
+        <v>0.285695</v>
       </c>
       <c r="P14" t="n">
-        <v>0.425397</v>
+        <v>1.039024</v>
       </c>
       <c r="Q14" t="n">
-        <v>126.96</v>
+        <v>130.07</v>
       </c>
       <c r="R14" t="n">
-        <v>115.07</v>
+        <v>120.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0.310915</v>
+        <v>0.563867</v>
       </c>
     </row>
     <row r="15">
@@ -5753,25 +5403,25 @@
         <v>0.421436</v>
       </c>
       <c r="M17" t="n">
-        <v>4.768</v>
+        <v>6.416</v>
       </c>
       <c r="N17" t="n">
-        <v>0.186944</v>
+        <v>0.208956</v>
       </c>
       <c r="O17" t="n">
-        <v>0.262188</v>
+        <v>0.288301</v>
       </c>
       <c r="P17" t="n">
-        <v>0.891243</v>
+        <v>1.340479</v>
       </c>
       <c r="Q17" t="n">
-        <v>131.45</v>
+        <v>127.55</v>
       </c>
       <c r="R17" t="n">
-        <v>121.72</v>
+        <v>117.49</v>
       </c>
       <c r="S17" t="n">
-        <v>0.47216</v>
+        <v>0.496513</v>
       </c>
     </row>
     <row r="18">
@@ -5927,46 +5577,46 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>5.242</v>
+        <v>5.6311</v>
       </c>
       <c r="G20" t="n">
-        <v>0.172767</v>
+        <v>0.167237</v>
       </c>
       <c r="H20" t="n">
-        <v>0.226691</v>
+        <v>0.222755</v>
       </c>
       <c r="I20" t="n">
-        <v>0.910588</v>
+        <v>0.946036</v>
       </c>
       <c r="J20" t="n">
-        <v>95.2</v>
+        <v>92.87</v>
       </c>
       <c r="K20" t="n">
-        <v>75.86</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.498638</v>
+        <v>0.528369</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.061037</v>
+        <v>0.09478499999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.082415</v>
+        <v>0.126718</v>
       </c>
       <c r="P20" t="n">
-        <v>0.182899</v>
+        <v>0.568213</v>
       </c>
       <c r="Q20" t="n">
-        <v>97.17</v>
+        <v>103.32</v>
       </c>
       <c r="R20" t="n">
-        <v>94.34999999999999</v>
+        <v>100.54</v>
       </c>
       <c r="S20" t="n">
-        <v>0.150054</v>
+        <v>0.281716</v>
       </c>
     </row>
     <row r="21">
@@ -6143,25 +5793,25 @@
         <v>0.447089</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2383</v>
+        <v>6.3076</v>
       </c>
       <c r="N23" t="n">
-        <v>0.09804599999999999</v>
+        <v>0.114737</v>
       </c>
       <c r="O23" t="n">
-        <v>0.130734</v>
+        <v>0.152943</v>
       </c>
       <c r="P23" t="n">
-        <v>0.415059</v>
+        <v>0.721834</v>
       </c>
       <c r="Q23" t="n">
-        <v>102.64</v>
+        <v>104.86</v>
       </c>
       <c r="R23" t="n">
-        <v>97.36</v>
+        <v>101.63</v>
       </c>
       <c r="S23" t="n">
-        <v>0.20937</v>
+        <v>0.32947</v>
       </c>
     </row>
     <row r="24">
@@ -6338,25 +5988,25 @@
         <v>0.451181</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9844</v>
+        <v>5.628</v>
       </c>
       <c r="N26" t="n">
-        <v>0.071842</v>
+        <v>0.078426</v>
       </c>
       <c r="O26" t="n">
-        <v>0.096565</v>
+        <v>0.105669</v>
       </c>
       <c r="P26" t="n">
-        <v>0.357759</v>
+        <v>0.440693</v>
       </c>
       <c r="Q26" t="n">
-        <v>124.74</v>
+        <v>128.25</v>
       </c>
       <c r="R26" t="n">
-        <v>110.26</v>
+        <v>112.88</v>
       </c>
       <c r="S26" t="n">
-        <v>0.158746</v>
+        <v>0.189814</v>
       </c>
     </row>
     <row r="27">
@@ -6923,25 +6573,25 @@
         <v>0.445217</v>
       </c>
       <c r="M35" t="n">
-        <v>4.96</v>
+        <v>5.672</v>
       </c>
       <c r="N35" t="n">
-        <v>0.171941</v>
+        <v>0.178435</v>
       </c>
       <c r="O35" t="n">
-        <v>0.23295</v>
+        <v>0.243534</v>
       </c>
       <c r="P35" t="n">
-        <v>0.852827</v>
+        <v>1.011885</v>
       </c>
       <c r="Q35" t="n">
-        <v>129.71</v>
+        <v>128.05</v>
       </c>
       <c r="R35" t="n">
-        <v>117.6</v>
+        <v>116.31</v>
       </c>
       <c r="S35" t="n">
-        <v>0.45936</v>
+        <v>0.478269</v>
       </c>
     </row>
     <row r="36">
@@ -7097,46 +6747,46 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>4.0023</v>
+        <v>6.0353</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03306</v>
+        <v>0.041381</v>
       </c>
       <c r="H38" t="n">
-        <v>0.042714</v>
+        <v>0.0542</v>
       </c>
       <c r="I38" t="n">
-        <v>0.132643</v>
+        <v>0.249722</v>
       </c>
       <c r="J38" t="n">
-        <v>111.48</v>
+        <v>117.82</v>
       </c>
       <c r="K38" t="n">
-        <v>88.23</v>
+        <v>95.33</v>
       </c>
       <c r="L38" t="n">
-        <v>0.06399299999999999</v>
+        <v>0.140312</v>
       </c>
       <c r="M38" t="n">
-        <v>6.4766</v>
+        <v>6.875</v>
       </c>
       <c r="N38" t="n">
-        <v>0.029371</v>
+        <v>0.030217</v>
       </c>
       <c r="O38" t="n">
-        <v>0.038034</v>
+        <v>0.039477</v>
       </c>
       <c r="P38" t="n">
-        <v>0.190048</v>
+        <v>0.207464</v>
       </c>
       <c r="Q38" t="n">
-        <v>92.39</v>
+        <v>92.31</v>
       </c>
       <c r="R38" t="n">
-        <v>85.81999999999999</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="S38" t="n">
-        <v>0.07438599999999999</v>
+        <v>0.077517</v>
       </c>
     </row>
     <row r="39">
@@ -7313,25 +6963,25 @@
         <v>0.092262</v>
       </c>
       <c r="M41" t="n">
-        <v>5.2266</v>
+        <v>5.3907</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01858</v>
+        <v>0.018713</v>
       </c>
       <c r="O41" t="n">
-        <v>0.023931</v>
+        <v>0.02416</v>
       </c>
       <c r="P41" t="n">
-        <v>0.096834</v>
+        <v>0.09998799999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>118.72</v>
+        <v>118.33</v>
       </c>
       <c r="R41" t="n">
-        <v>99.09</v>
+        <v>98.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0.039551</v>
+        <v>0.040669</v>
       </c>
     </row>
     <row r="42">
@@ -7508,25 +7158,25 @@
         <v>0.092568</v>
       </c>
       <c r="M44" t="n">
-        <v>5.4609</v>
+        <v>5.9375</v>
       </c>
       <c r="N44" t="n">
-        <v>0.019347</v>
+        <v>0.019176</v>
       </c>
       <c r="O44" t="n">
-        <v>0.024897</v>
+        <v>0.024712</v>
       </c>
       <c r="P44" t="n">
-        <v>0.105615</v>
+        <v>0.113268</v>
       </c>
       <c r="Q44" t="n">
-        <v>108.58</v>
+        <v>107.62</v>
       </c>
       <c r="R44" t="n">
-        <v>88.14</v>
+        <v>85.89</v>
       </c>
       <c r="S44" t="n">
-        <v>0.035493</v>
+        <v>0.03643</v>
       </c>
     </row>
     <row r="45">
@@ -7703,25 +7353,25 @@
         <v>0.077454</v>
       </c>
       <c r="M47" t="n">
-        <v>6.232</v>
+        <v>6.472</v>
       </c>
       <c r="N47" t="n">
-        <v>0.041665</v>
+        <v>0.041275</v>
       </c>
       <c r="O47" t="n">
-        <v>0.055055</v>
+        <v>0.054692</v>
       </c>
       <c r="P47" t="n">
-        <v>0.259577</v>
+        <v>0.267081</v>
       </c>
       <c r="Q47" t="n">
-        <v>112.81</v>
+        <v>111.88</v>
       </c>
       <c r="R47" t="n">
-        <v>96.2</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="S47" t="n">
-        <v>0.112626</v>
+        <v>0.110709</v>
       </c>
     </row>
     <row r="48">
@@ -7898,25 +7548,25 @@
         <v>0.09902900000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>6.528</v>
+        <v>7.176</v>
       </c>
       <c r="N50" t="n">
-        <v>0.038082</v>
+        <v>0.038906</v>
       </c>
       <c r="O50" t="n">
-        <v>0.049865</v>
+        <v>0.051647</v>
       </c>
       <c r="P50" t="n">
-        <v>0.248199</v>
+        <v>0.278715</v>
       </c>
       <c r="Q50" t="n">
-        <v>115.94</v>
+        <v>115.66</v>
       </c>
       <c r="R50" t="n">
-        <v>99.48999999999999</v>
+        <v>99.89</v>
       </c>
       <c r="S50" t="n">
-        <v>0.110116</v>
+        <v>0.10955</v>
       </c>
     </row>
     <row r="51">
@@ -8072,46 +7722,46 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>2.7635</v>
+        <v>5.4238</v>
       </c>
       <c r="G53" t="n">
-        <v>0.030277</v>
+        <v>0.034039</v>
       </c>
       <c r="H53" t="n">
-        <v>0.03871</v>
+        <v>0.043688</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08339299999999999</v>
+        <v>0.184366</v>
       </c>
       <c r="J53" t="n">
-        <v>101.38</v>
+        <v>111.7</v>
       </c>
       <c r="K53" t="n">
-        <v>83.01000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="L53" t="n">
-        <v>0.058036</v>
+        <v>0.066971</v>
       </c>
       <c r="M53" t="n">
-        <v>5.6953</v>
+        <v>5.8779</v>
       </c>
       <c r="N53" t="n">
-        <v>0.030453</v>
+        <v>0.031684</v>
       </c>
       <c r="O53" t="n">
-        <v>0.038049</v>
+        <v>0.039551</v>
       </c>
       <c r="P53" t="n">
-        <v>0.171391</v>
+        <v>0.185178</v>
       </c>
       <c r="Q53" t="n">
-        <v>63.49</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="R53" t="n">
-        <v>51.39</v>
+        <v>53.78</v>
       </c>
       <c r="S53" t="n">
-        <v>0.07747900000000001</v>
+        <v>0.07588499999999999</v>
       </c>
     </row>
     <row r="54">
@@ -8158,25 +7808,25 @@
         <v>0.075061</v>
       </c>
       <c r="M54" t="n">
-        <v>2.0859</v>
+        <v>6.0273</v>
       </c>
       <c r="N54" t="n">
-        <v>0.026656</v>
+        <v>0.0269</v>
       </c>
       <c r="O54" t="n">
-        <v>0.034089</v>
+        <v>0.034069</v>
       </c>
       <c r="P54" t="n">
-        <v>0.053283</v>
+        <v>0.159539</v>
       </c>
       <c r="Q54" t="n">
-        <v>68.47</v>
+        <v>62.75</v>
       </c>
       <c r="R54" t="n">
-        <v>52.41</v>
+        <v>49.39</v>
       </c>
       <c r="S54" t="n">
-        <v>0.043912</v>
+        <v>0.046021</v>
       </c>
     </row>
     <row r="55">
@@ -8223,25 +7873,25 @@
         <v>0.050086</v>
       </c>
       <c r="M55" t="n">
-        <v>0.6797</v>
+        <v>6.3759</v>
       </c>
       <c r="N55" t="n">
-        <v>0.036437</v>
+        <v>0.027279</v>
       </c>
       <c r="O55" t="n">
-        <v>0.040534</v>
+        <v>0.034296</v>
       </c>
       <c r="P55" t="n">
-        <v>0.023446</v>
+        <v>0.172943</v>
       </c>
       <c r="Q55" t="n">
-        <v>22.83</v>
+        <v>59.28</v>
       </c>
       <c r="R55" t="n">
-        <v>9.68</v>
+        <v>47.43</v>
       </c>
       <c r="S55" t="n">
-        <v>0.061197</v>
+        <v>0.061549</v>
       </c>
     </row>
     <row r="56">
@@ -8288,25 +7938,25 @@
         <v>0.051698</v>
       </c>
       <c r="M56" t="n">
-        <v>1.4765</v>
+        <v>1.6445</v>
       </c>
       <c r="N56" t="n">
-        <v>0.029666</v>
+        <v>0.03578</v>
       </c>
       <c r="O56" t="n">
-        <v>0.035233</v>
+        <v>0.042011</v>
       </c>
       <c r="P56" t="n">
-        <v>0.042086</v>
+        <v>0.057992</v>
       </c>
       <c r="Q56" t="n">
-        <v>31.65</v>
+        <v>24.59</v>
       </c>
       <c r="R56" t="n">
-        <v>16.49</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
-        <v>0.057386</v>
+        <v>0.059413</v>
       </c>
     </row>
     <row r="57">
@@ -8353,25 +8003,25 @@
         <v>0.071741</v>
       </c>
       <c r="M57" t="n">
-        <v>5.9922</v>
+        <v>6.376</v>
       </c>
       <c r="N57" t="n">
-        <v>0.027328</v>
+        <v>0.027245</v>
       </c>
       <c r="O57" t="n">
-        <v>0.03468</v>
+        <v>0.034674</v>
       </c>
       <c r="P57" t="n">
-        <v>0.162935</v>
+        <v>0.172554</v>
       </c>
       <c r="Q57" t="n">
-        <v>65.25</v>
+        <v>64.78</v>
       </c>
       <c r="R57" t="n">
-        <v>54.17</v>
+        <v>53.52</v>
       </c>
       <c r="S57" t="n">
-        <v>0.061665</v>
+        <v>0.061879</v>
       </c>
     </row>
     <row r="58">
@@ -8418,25 +8068,25 @@
         <v>0.06601799999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>6.1094</v>
+        <v>6.5752</v>
       </c>
       <c r="N58" t="n">
-        <v>0.027747</v>
+        <v>0.027561</v>
       </c>
       <c r="O58" t="n">
-        <v>0.034935</v>
+        <v>0.034946</v>
       </c>
       <c r="P58" t="n">
-        <v>0.168331</v>
+        <v>0.18113</v>
       </c>
       <c r="Q58" t="n">
-        <v>61</v>
+        <v>61.66</v>
       </c>
       <c r="R58" t="n">
-        <v>49.53</v>
+        <v>49.84</v>
       </c>
       <c r="S58" t="n">
-        <v>0.068217</v>
+        <v>0.06838900000000001</v>
       </c>
     </row>
     <row r="59">
@@ -8831,25 +8481,25 @@
         <v>0.046947</v>
       </c>
       <c r="M65" t="n">
-        <v>5.76</v>
+        <v>6.28</v>
       </c>
       <c r="N65" t="n">
-        <v>0.0242</v>
+        <v>0.024093</v>
       </c>
       <c r="O65" t="n">
-        <v>0.031836</v>
+        <v>0.031455</v>
       </c>
       <c r="P65" t="n">
-        <v>0.139286</v>
+        <v>0.151163</v>
       </c>
       <c r="Q65" t="n">
-        <v>127.04</v>
+        <v>125.53</v>
       </c>
       <c r="R65" t="n">
-        <v>106.79</v>
+        <v>105.56</v>
       </c>
       <c r="S65" t="n">
-        <v>0.054873</v>
+        <v>0.055541</v>
       </c>
     </row>
     <row r="66">
@@ -9026,25 +8676,25 @@
         <v>0.037672</v>
       </c>
       <c r="M68" t="n">
-        <v>4.232</v>
+        <v>5.488</v>
       </c>
       <c r="N68" t="n">
-        <v>0.017431</v>
+        <v>0.018626</v>
       </c>
       <c r="O68" t="n">
-        <v>0.023105</v>
+        <v>0.024714</v>
       </c>
       <c r="P68" t="n">
-        <v>0.073744</v>
+        <v>0.102152</v>
       </c>
       <c r="Q68" t="n">
-        <v>128.25</v>
+        <v>128.89</v>
       </c>
       <c r="R68" t="n">
-        <v>106.04</v>
+        <v>107.25</v>
       </c>
       <c r="S68" t="n">
-        <v>0.035766</v>
+        <v>0.040293</v>
       </c>
     </row>
     <row r="69">
@@ -9200,46 +8850,46 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>5.2637</v>
+        <v>6.2246</v>
       </c>
       <c r="G71" t="n">
-        <v>0.142313</v>
+        <v>0.147727</v>
       </c>
       <c r="H71" t="n">
-        <v>0.188922</v>
+        <v>0.200645</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7485309999999999</v>
+        <v>0.919345</v>
       </c>
       <c r="J71" t="n">
-        <v>112.19</v>
+        <v>109.9</v>
       </c>
       <c r="K71" t="n">
-        <v>108.75</v>
+        <v>106.03</v>
       </c>
       <c r="L71" t="n">
-        <v>0.315783</v>
+        <v>0.399139</v>
       </c>
       <c r="M71" t="n">
-        <v>5.8701</v>
+        <v>6.791</v>
       </c>
       <c r="N71" t="n">
-        <v>0.115144</v>
+        <v>0.128422</v>
       </c>
       <c r="O71" t="n">
-        <v>0.152303</v>
+        <v>0.169564</v>
       </c>
       <c r="P71" t="n">
-        <v>0.675385</v>
+        <v>0.870947</v>
       </c>
       <c r="Q71" t="n">
-        <v>95.2</v>
+        <v>94.19</v>
       </c>
       <c r="R71" t="n">
-        <v>90.31999999999999</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="S71" t="n">
-        <v>0.276122</v>
+        <v>0.372059</v>
       </c>
     </row>
     <row r="72">
@@ -9395,46 +9045,46 @@
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>0.061037</v>
+        <v>0.09478499999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.082415</v>
+        <v>0.126718</v>
       </c>
       <c r="I74" t="n">
-        <v>0.182899</v>
+        <v>0.568213</v>
       </c>
       <c r="J74" t="n">
-        <v>97.17</v>
+        <v>103.32</v>
       </c>
       <c r="K74" t="n">
-        <v>94.34999999999999</v>
+        <v>100.54</v>
       </c>
       <c r="L74" t="n">
-        <v>0.150054</v>
+        <v>0.281716</v>
       </c>
       <c r="M74" t="n">
-        <v>4.6133</v>
+        <v>5.2744</v>
       </c>
       <c r="N74" t="n">
-        <v>0.121979</v>
+        <v>0.138856</v>
       </c>
       <c r="O74" t="n">
-        <v>0.164965</v>
+        <v>0.186907</v>
       </c>
       <c r="P74" t="n">
-        <v>0.562292</v>
+        <v>0.730566</v>
       </c>
       <c r="Q74" t="n">
-        <v>101.23</v>
+        <v>102.38</v>
       </c>
       <c r="R74" t="n">
-        <v>97.75</v>
+        <v>98.77</v>
       </c>
       <c r="S74" t="n">
-        <v>0.26955</v>
+        <v>0.377634</v>
       </c>
     </row>
     <row r="75">
@@ -9590,46 +9240,46 @@
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>6.4766</v>
+        <v>6.875</v>
       </c>
       <c r="G77" t="n">
-        <v>0.029371</v>
+        <v>0.030217</v>
       </c>
       <c r="H77" t="n">
-        <v>0.038034</v>
+        <v>0.039477</v>
       </c>
       <c r="I77" t="n">
-        <v>0.190048</v>
+        <v>0.207464</v>
       </c>
       <c r="J77" t="n">
-        <v>92.39</v>
+        <v>92.31</v>
       </c>
       <c r="K77" t="n">
-        <v>85.81999999999999</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>0.07438599999999999</v>
+        <v>0.077517</v>
       </c>
       <c r="M77" t="n">
-        <v>6.6172</v>
+        <v>6.8672</v>
       </c>
       <c r="N77" t="n">
-        <v>0.017699</v>
+        <v>0.017895</v>
       </c>
       <c r="O77" t="n">
-        <v>0.022209</v>
+        <v>0.022532</v>
       </c>
       <c r="P77" t="n">
-        <v>0.116736</v>
+        <v>0.12247</v>
       </c>
       <c r="Q77" t="n">
-        <v>80.59999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="R77" t="n">
-        <v>69.90000000000001</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="S77" t="n">
-        <v>0.038419</v>
+        <v>0.038313</v>
       </c>
     </row>
     <row r="78">
@@ -9785,46 +9435,46 @@
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>5.6953</v>
+        <v>5.8779</v>
       </c>
       <c r="G80" t="n">
-        <v>0.030453</v>
+        <v>0.031684</v>
       </c>
       <c r="H80" t="n">
-        <v>0.038049</v>
+        <v>0.039551</v>
       </c>
       <c r="I80" t="n">
-        <v>0.171391</v>
+        <v>0.185178</v>
       </c>
       <c r="J80" t="n">
-        <v>63.49</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>51.39</v>
+        <v>53.78</v>
       </c>
       <c r="L80" t="n">
-        <v>0.07747900000000001</v>
+        <v>0.07588499999999999</v>
       </c>
       <c r="M80" t="n">
-        <v>5.75</v>
+        <v>6.0703</v>
       </c>
       <c r="N80" t="n">
-        <v>0.025321</v>
+        <v>0.027127</v>
       </c>
       <c r="O80" t="n">
-        <v>0.030373</v>
+        <v>0.032611</v>
       </c>
       <c r="P80" t="n">
-        <v>0.144156</v>
+        <v>0.161167</v>
       </c>
       <c r="Q80" t="n">
-        <v>82.56999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="R80" t="n">
-        <v>75.90000000000001</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="S80" t="n">
-        <v>0.097778</v>
+        <v>0.098286</v>
       </c>
     </row>
     <row r="81">
@@ -9850,25 +9500,25 @@
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2.0859</v>
+        <v>6.0273</v>
       </c>
       <c r="G81" t="n">
-        <v>0.026656</v>
+        <v>0.0269</v>
       </c>
       <c r="H81" t="n">
-        <v>0.034089</v>
+        <v>0.034069</v>
       </c>
       <c r="I81" t="n">
-        <v>0.053283</v>
+        <v>0.159539</v>
       </c>
       <c r="J81" t="n">
-        <v>68.47</v>
+        <v>62.75</v>
       </c>
       <c r="K81" t="n">
-        <v>52.41</v>
+        <v>49.39</v>
       </c>
       <c r="L81" t="n">
-        <v>0.043912</v>
+        <v>0.046021</v>
       </c>
       <c r="M81" t="n">
         <v>6.5626</v>
@@ -9915,25 +9565,25 @@
         <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6797</v>
+        <v>6.3759</v>
       </c>
       <c r="G82" t="n">
-        <v>0.036437</v>
+        <v>0.027279</v>
       </c>
       <c r="H82" t="n">
-        <v>0.040534</v>
+        <v>0.034296</v>
       </c>
       <c r="I82" t="n">
-        <v>0.023446</v>
+        <v>0.172943</v>
       </c>
       <c r="J82" t="n">
-        <v>22.83</v>
+        <v>59.28</v>
       </c>
       <c r="K82" t="n">
-        <v>9.68</v>
+        <v>47.43</v>
       </c>
       <c r="L82" t="n">
-        <v>0.061197</v>
+        <v>0.061549</v>
       </c>
       <c r="M82" t="n">
         <v>6.6641</v>
@@ -10001,25 +9651,25 @@
         <v>0.374563</v>
       </c>
       <c r="M83" t="n">
-        <v>5.7422</v>
+        <v>6.8203</v>
       </c>
       <c r="N83" t="n">
-        <v>0.101359</v>
+        <v>0.111792</v>
       </c>
       <c r="O83" t="n">
-        <v>0.129165</v>
+        <v>0.144284</v>
       </c>
       <c r="P83" t="n">
-        <v>0.580485</v>
+        <v>0.75829</v>
       </c>
       <c r="Q83" t="n">
-        <v>80.68000000000001</v>
+        <v>83.19</v>
       </c>
       <c r="R83" t="n">
-        <v>73.44</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="S83" t="n">
-        <v>0.301568</v>
+        <v>0.342984</v>
       </c>
     </row>
     <row r="84">
@@ -10630,25 +10280,25 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>10.4434</v>
+        <v>12.5081</v>
       </c>
       <c r="G93" t="n">
-        <v>0.095166</v>
+        <v>0.083896</v>
       </c>
       <c r="H93" t="n">
-        <v>0.131385</v>
+        <v>0.115653</v>
       </c>
       <c r="I93" t="n">
-        <v>0.999024</v>
+        <v>1.054571</v>
       </c>
       <c r="J93" t="n">
-        <v>140.01</v>
+        <v>135.98</v>
       </c>
       <c r="K93" t="n">
-        <v>118.15</v>
+        <v>114.34</v>
       </c>
       <c r="L93" t="n">
-        <v>0.356462</v>
+        <v>0.386078</v>
       </c>
       <c r="M93" t="n">
         <v>1.8477</v>
@@ -11301,25 +10951,25 @@
         <v>1.16481</v>
       </c>
       <c r="M103" t="n">
-        <v>8.265599999999999</v>
+        <v>9.109400000000001</v>
       </c>
       <c r="N103" t="n">
-        <v>0.082548</v>
+        <v>0.090155</v>
       </c>
       <c r="O103" t="n">
-        <v>0.10714</v>
+        <v>0.117432</v>
       </c>
       <c r="P103" t="n">
-        <v>0.680482</v>
+        <v>0.819708</v>
       </c>
       <c r="Q103" t="n">
-        <v>82.11</v>
+        <v>82.95</v>
       </c>
       <c r="R103" t="n">
-        <v>74.93000000000001</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="S103" t="n">
-        <v>0.22908</v>
+        <v>0.285645</v>
       </c>
     </row>
     <row r="104">
@@ -11951,25 +11601,25 @@
         <v>0.375975</v>
       </c>
       <c r="M113" t="n">
-        <v>4.9111</v>
+        <v>5.6455</v>
       </c>
       <c r="N113" t="n">
-        <v>0.13663</v>
+        <v>0.136873</v>
       </c>
       <c r="O113" t="n">
-        <v>0.180462</v>
+        <v>0.182505</v>
       </c>
       <c r="P113" t="n">
-        <v>0.669438</v>
+        <v>0.771359</v>
       </c>
       <c r="Q113" t="n">
-        <v>101.58</v>
+        <v>100.45</v>
       </c>
       <c r="R113" t="n">
-        <v>95.72</v>
+        <v>95.23</v>
       </c>
       <c r="S113" t="n">
-        <v>0.312494</v>
+        <v>0.32796</v>
       </c>
     </row>
     <row r="114">
@@ -12601,25 +12251,25 @@
         <v>0.289998</v>
       </c>
       <c r="M123" t="n">
-        <v>4.9922</v>
+        <v>5.5625</v>
       </c>
       <c r="N123" t="n">
-        <v>0.107175</v>
+        <v>0.111023</v>
       </c>
       <c r="O123" t="n">
-        <v>0.141004</v>
+        <v>0.148111</v>
       </c>
       <c r="P123" t="n">
-        <v>0.534729</v>
+        <v>0.616478</v>
       </c>
       <c r="Q123" t="n">
-        <v>103.02</v>
+        <v>101.54</v>
       </c>
       <c r="R123" t="n">
-        <v>98.27</v>
+        <v>96.67</v>
       </c>
       <c r="S123" t="n">
-        <v>0.24967</v>
+        <v>0.324172</v>
       </c>
     </row>
     <row r="124">
@@ -13251,25 +12901,25 @@
         <v>0.296093</v>
       </c>
       <c r="M133" t="n">
-        <v>4.8662</v>
+        <v>5.5615</v>
       </c>
       <c r="N133" t="n">
-        <v>0.116361</v>
+        <v>0.117545</v>
       </c>
       <c r="O133" t="n">
-        <v>0.1554</v>
+        <v>0.158394</v>
       </c>
       <c r="P133" t="n">
-        <v>0.56595</v>
+        <v>0.652217</v>
       </c>
       <c r="Q133" t="n">
-        <v>101.76</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="R133" t="n">
-        <v>97.69</v>
+        <v>94.31</v>
       </c>
       <c r="S133" t="n">
-        <v>0.274211</v>
+        <v>0.281779</v>
       </c>
     </row>
     <row r="134">
@@ -14530,46 +14180,46 @@
         <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>1.3579</v>
+        <v>4.3533</v>
       </c>
       <c r="G153" t="n">
-        <v>0.024242</v>
+        <v>0.024973</v>
       </c>
       <c r="H153" t="n">
-        <v>0.031356</v>
+        <v>0.032464</v>
       </c>
       <c r="I153" t="n">
-        <v>0.030944</v>
+        <v>0.109172</v>
       </c>
       <c r="J153" t="n">
-        <v>108.94</v>
+        <v>117.19</v>
       </c>
       <c r="K153" t="n">
-        <v>91.84</v>
+        <v>94.62</v>
       </c>
       <c r="L153" t="n">
-        <v>0.042091</v>
+        <v>0.045904</v>
       </c>
       <c r="M153" t="n">
-        <v>6.6172</v>
+        <v>6.9453</v>
       </c>
       <c r="N153" t="n">
-        <v>0.018624</v>
+        <v>0.018762</v>
       </c>
       <c r="O153" t="n">
-        <v>0.024175</v>
+        <v>0.024394</v>
       </c>
       <c r="P153" t="n">
-        <v>0.123024</v>
+        <v>0.13031</v>
       </c>
       <c r="Q153" t="n">
-        <v>83.59999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="R153" t="n">
-        <v>74.39</v>
+        <v>73.87</v>
       </c>
       <c r="S153" t="n">
-        <v>0.046184</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="154">
@@ -15201,25 +14851,25 @@
         <v>0.076261</v>
       </c>
       <c r="M163" t="n">
-        <v>5.9609</v>
+        <v>6.7187</v>
       </c>
       <c r="N163" t="n">
-        <v>0.020439</v>
+        <v>0.020911</v>
       </c>
       <c r="O163" t="n">
-        <v>0.025968</v>
+        <v>0.026537</v>
       </c>
       <c r="P163" t="n">
-        <v>0.121751</v>
+        <v>0.140282</v>
       </c>
       <c r="Q163" t="n">
-        <v>82.95999999999999</v>
+        <v>80.37</v>
       </c>
       <c r="R163" t="n">
-        <v>74.34999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="S163" t="n">
-        <v>0.038448</v>
+        <v>0.042168</v>
       </c>
     </row>
     <row r="164">
@@ -15851,25 +15501,25 @@
         <v>0.06512900000000001</v>
       </c>
       <c r="M173" t="n">
-        <v>6.1719</v>
+        <v>6.5</v>
       </c>
       <c r="N173" t="n">
-        <v>0.027783</v>
+        <v>0.030387</v>
       </c>
       <c r="O173" t="n">
-        <v>0.033053</v>
+        <v>0.035947</v>
       </c>
       <c r="P173" t="n">
-        <v>0.168994</v>
+        <v>0.196223</v>
       </c>
       <c r="Q173" t="n">
-        <v>75.73999999999999</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="R173" t="n">
-        <v>68.73999999999999</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="S173" t="n">
-        <v>0.103401</v>
+        <v>0.111622</v>
       </c>
     </row>
     <row r="174">
@@ -16501,25 +16151,25 @@
         <v>0.053705</v>
       </c>
       <c r="M183" t="n">
-        <v>4.2969</v>
+        <v>4.7422</v>
       </c>
       <c r="N183" t="n">
-        <v>0.018445</v>
+        <v>0.022929</v>
       </c>
       <c r="O183" t="n">
-        <v>0.02344</v>
+        <v>0.027823</v>
       </c>
       <c r="P183" t="n">
-        <v>0.07835499999999999</v>
+        <v>0.108413</v>
       </c>
       <c r="Q183" t="n">
-        <v>97.84</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R183" t="n">
-        <v>94.98</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S183" t="n">
-        <v>0.034068</v>
+        <v>0.091859</v>
       </c>
     </row>
     <row r="184">
@@ -17151,25 +16801,25 @@
         <v>0.063736</v>
       </c>
       <c r="M193" t="n">
-        <v>6.1641</v>
+        <v>6.7188</v>
       </c>
       <c r="N193" t="n">
-        <v>0.023157</v>
+        <v>0.025117</v>
       </c>
       <c r="O193" t="n">
-        <v>0.027794</v>
+        <v>0.029999</v>
       </c>
       <c r="P193" t="n">
-        <v>0.140778</v>
+        <v>0.168336</v>
       </c>
       <c r="Q193" t="n">
-        <v>78.34</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="R193" t="n">
-        <v>70.45</v>
+        <v>69.28</v>
       </c>
       <c r="S193" t="n">
-        <v>0.110003</v>
+        <v>0.110167</v>
       </c>
     </row>
     <row r="194">
@@ -17841,10 +17491,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0454</v>
+        <v>0.9744</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0371</v>
+        <v>0.9708</v>
       </c>
     </row>
     <row r="3">
@@ -17875,10 +17525,10 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.972</v>
+        <v>0.9999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1826</v>
+        <v>0.2479</v>
       </c>
     </row>
     <row r="4">
@@ -17909,10 +17559,10 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8403</v>
+        <v>0.9984</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0459</v>
+        <v>0.4438</v>
       </c>
     </row>
     <row r="5">
@@ -17943,10 +17593,10 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6936</v>
+        <v>0.9597</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0953</v>
+        <v>0.1897</v>
       </c>
     </row>
     <row r="6">
@@ -17977,10 +17627,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7448</v>
+        <v>-0.6715</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1042</v>
+        <v>-0.0625</v>
       </c>
     </row>
     <row r="7">
@@ -18011,10 +17661,10 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4223</v>
+        <v>0.5065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0086</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="8">
@@ -18045,10 +17695,10 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.909</v>
+        <v>0.8348</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1401</v>
+        <v>0.1771</v>
       </c>
     </row>
     <row r="9">
@@ -18079,10 +17729,10 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9804</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9201</v>
+        <v>0.9461000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -18113,10 +17763,10 @@
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9512</v>
+        <v>0.895</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5254</v>
+        <v>0.6465</v>
       </c>
     </row>
     <row r="11">
@@ -18147,10 +17797,10 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9155</v>
+        <v>0.8928</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1797</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="12">
@@ -18181,10 +17831,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9523</v>
+        <v>0.8899</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4956</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="13">
@@ -18215,10 +17865,10 @@
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8507</v>
+        <v>0.9107</v>
       </c>
       <c r="H13" t="n">
-        <v>0.852</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="14">
@@ -18249,10 +17899,10 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9365</v>
+        <v>0.9731</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2556</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="15">
@@ -18283,10 +17933,10 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0161</v>
+        <v>-0.6866</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0016</v>
+        <v>-0.1821</v>
       </c>
     </row>
     <row r="16">
@@ -18317,10 +17967,10 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8317</v>
+        <v>0.9968</v>
       </c>
       <c r="H16" t="n">
-        <v>0.833</v>
+        <v>0.8544</v>
       </c>
     </row>
     <row r="17">
@@ -18351,10 +18001,10 @@
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7393</v>
+        <v>0.8954</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0117</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="18">
@@ -18385,10 +18035,10 @@
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8706</v>
+        <v>0.8647</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0135</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="19">
@@ -18419,10 +18069,10 @@
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6493</v>
+        <v>0.8285</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0089</v>
+        <v>0.0102</v>
       </c>
     </row>
     <row r="20">
@@ -18453,10 +18103,10 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9777</v>
+        <v>0.9969</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1926</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="21">
@@ -18487,10 +18137,10 @@
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8113</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="22">
@@ -18521,10 +18171,10 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.945</v>
+        <v>0.7339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0187</v>
+        <v>0.0076</v>
       </c>
     </row>
     <row r="23">
@@ -18555,10 +18205,10 @@
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5845</v>
+        <v>0.989</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3591</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="24">
@@ -18589,10 +18239,10 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.855</v>
+        <v>0.9876</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0021</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="25">
@@ -18623,10 +18273,10 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8839</v>
+        <v>0.9848</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0205</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="26">
@@ -18657,10 +18307,10 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9321</v>
+        <v>0.9764</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0039</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -18691,10 +18341,10 @@
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9525</v>
+        <v>0.8798</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2347</v>
+        <v>0.1836</v>
       </c>
     </row>
     <row r="28">
@@ -18725,10 +18375,10 @@
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9982</v>
+        <v>0.9805</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6076</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="29">
@@ -18759,10 +18409,10 @@
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4962</v>
+        <v>0.7791</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0135</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="30">
@@ -18793,10 +18443,10 @@
         <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3695</v>
+        <v>0.1792</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0563</v>
+        <v>0.09420000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -18827,10 +18477,10 @@
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6254</v>
+        <v>0.7215</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7902</v>
+        <v>0.2835</v>
       </c>
     </row>
     <row r="32">
@@ -18861,10 +18511,10 @@
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7684</v>
+        <v>0.6865</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4574</v>
+        <v>0.3774</v>
       </c>
     </row>
     <row r="33">
@@ -18895,10 +18545,10 @@
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4749</v>
+        <v>0.8094</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5168</v>
+        <v>0.2975</v>
       </c>
     </row>
     <row r="34">
@@ -18929,10 +18579,10 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2726</v>
+        <v>0.328</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.075</v>
+        <v>0.0861</v>
       </c>
     </row>
     <row r="35">
@@ -18963,10 +18613,10 @@
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0521</v>
+        <v>0.4936</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0072</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="36">
@@ -18997,10 +18647,10 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7138</v>
+        <v>-0.2479</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6076</v>
+        <v>-0.0347</v>
       </c>
     </row>
     <row r="37">
@@ -19031,10 +18681,10 @@
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9631999999999999</v>
+        <v>0.9971</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3991</v>
+        <v>0.9195</v>
       </c>
     </row>
     <row r="38">
@@ -19065,10 +18715,10 @@
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6244</v>
+        <v>-0.2734</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1636</v>
+        <v>-0.0159</v>
       </c>
     </row>
     <row r="39">
@@ -19099,10 +18749,10 @@
         <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.9182</v>
+        <v>0.9842</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0894</v>
+        <v>0.3004</v>
       </c>
     </row>
     <row r="40">
@@ -19133,10 +18783,10 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7006</v>
+        <v>-0.5216</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0134</v>
       </c>
     </row>
     <row r="41">
@@ -19167,10 +18817,10 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8952</v>
+        <v>0.824</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0738</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="42">
@@ -19201,10 +18851,10 @@
         <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9616</v>
+        <v>0.9409</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0917</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="43">
@@ -19235,10 +18885,10 @@
         <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>0.6273</v>
+        <v>0.6378</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4171</v>
+        <v>0.3673</v>
       </c>
     </row>
     <row r="44">
@@ -19269,10 +18919,10 @@
         <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9371</v>
+        <v>0.9916</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4953</v>
+        <v>0.6079</v>
       </c>
     </row>
     <row r="45">
@@ -19303,10 +18953,10 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.573</v>
+        <v>0.8103</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.062</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="46">
@@ -19337,10 +18987,10 @@
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.104</v>
+        <v>0.2194</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0058</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="47">
@@ -19371,10 +19021,10 @@
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.4897</v>
+        <v>0.7672</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0552</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="48">
@@ -19405,10 +19055,10 @@
         <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0273</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0013</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="49">
@@ -19439,10 +19089,10 @@
         <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2042</v>
+        <v>0.9977</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0614</v>
+        <v>0.0969</v>
       </c>
     </row>
     <row r="50">
@@ -19473,10 +19123,10 @@
         <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.7978</v>
+        <v>0.5016</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0472</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="51">
@@ -19507,10 +19157,10 @@
         <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.4364</v>
+        <v>0.972</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3908</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="52">
@@ -19541,10 +19191,10 @@
         <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9161</v>
+        <v>0.6731</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0306</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="53">
@@ -19575,10 +19225,10 @@
         <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.9059</v>
+        <v>0.9919</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0365</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="54">
@@ -19609,10 +19259,10 @@
         <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>0.945</v>
+        <v>0.6876</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0406</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="55">
@@ -19643,10 +19293,10 @@
         <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5093</v>
+        <v>0.9972</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0145</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="56">
@@ -19677,10 +19327,10 @@
         <v>3</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4462</v>
+        <v>0.9362</v>
       </c>
       <c r="H56" t="n">
-        <v>0.047</v>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="57">
@@ -19711,10 +19361,10 @@
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7019</v>
+        <v>-0.9415</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0252</v>
+        <v>-0.0424</v>
       </c>
     </row>
     <row r="58">
@@ -19745,10 +19395,10 @@
         <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.8851</v>
+        <v>-0.4673</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.8167</v>
+        <v>-0.1143</v>
       </c>
     </row>
     <row r="59">
@@ -19779,10 +19429,10 @@
         <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8196</v>
+        <v>0.9964</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0028</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="60">
@@ -19813,10 +19463,10 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.9233</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.005</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="61">
@@ -19847,10 +19497,10 @@
         <v>3</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7936</v>
+        <v>0.9905</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0028</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="62">
@@ -19881,10 +19531,10 @@
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9673</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0083</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="63">
@@ -19915,10 +19565,10 @@
         <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0216</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="64">
@@ -19949,10 +19599,10 @@
         <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8042</v>
+        <v>0.9275</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0173</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="65">
@@ -20459,10 +20109,10 @@
         <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9931</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.7996</v>
+        <v>0.6309</v>
       </c>
     </row>
     <row r="80">
@@ -20493,10 +20143,10 @@
         <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5629</v>
+        <v>0.7815</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1142</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="81">
@@ -20527,10 +20177,10 @@
         <v>3</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8331</v>
+        <v>0.9997</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4926</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="82">
@@ -20561,10 +20211,10 @@
         <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5961</v>
+        <v>0.8287</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1069</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="83">
@@ -20595,10 +20245,10 @@
         <v>3</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7607</v>
+        <v>0.4394</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0057</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="84">
@@ -20629,10 +20279,10 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.997</v>
+        <v>0.9872</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0198</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="85">
@@ -20663,10 +20313,10 @@
         <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>0.98</v>
+        <v>0.998</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4526</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="86">
@@ -20697,10 +20347,10 @@
         <v>3</v>
       </c>
       <c r="G86" t="n">
-        <v>0.697</v>
+        <v>-0.7081</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2677</v>
+        <v>-0.0214</v>
       </c>
     </row>
     <row r="87">
@@ -20731,10 +20381,10 @@
         <v>3</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.9653</v>
+        <v>0.5251</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.1182</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="88">
@@ -20765,10 +20415,10 @@
         <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8464</v>
+        <v>0.1343</v>
       </c>
       <c r="H88" t="n">
-        <v>0.6329</v>
+        <v>0.1626</v>
       </c>
     </row>
     <row r="89">
@@ -20799,10 +20449,10 @@
         <v>3</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.9834000000000001</v>
+        <v>0.2717</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.1645</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="90">
@@ -20833,10 +20483,10 @@
         <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>0.2721</v>
+        <v>0.9705</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0604</v>
+        <v>0.2316</v>
       </c>
     </row>
     <row r="91">
@@ -20867,10 +20517,10 @@
         <v>3</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6831</v>
+        <v>0.8771</v>
       </c>
       <c r="H91" t="n">
-        <v>0.0238</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="92">
@@ -20901,10 +20551,10 @@
         <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2559</v>
+        <v>0.8442</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0769</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="93">
@@ -20935,10 +20585,10 @@
         <v>3</v>
       </c>
       <c r="G93" t="n">
-        <v>0.994</v>
+        <v>0.9691</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1904</v>
+        <v>0.2022</v>
       </c>
     </row>
     <row r="94">
@@ -20969,10 +20619,10 @@
         <v>3</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9538</v>
+        <v>0.9524</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0226</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="95">
@@ -21003,10 +20653,10 @@
         <v>3</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9962</v>
+        <v>0.9999</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0291</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="96">
@@ -21037,10 +20687,10 @@
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9942</v>
+        <v>0.9938</v>
       </c>
       <c r="H96" t="n">
-        <v>0.0263</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="97">
@@ -21071,10 +20721,10 @@
         <v>3</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9789</v>
+        <v>0.9736</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2387</v>
+        <v>0.2351</v>
       </c>
     </row>
     <row r="98">
@@ -21105,10 +20755,10 @@
         <v>3</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8903</v>
+        <v>0.8595</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0722</v>
+        <v>0.0668</v>
       </c>
     </row>
     <row r="99">
@@ -21139,10 +20789,10 @@
         <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8264</v>
+        <v>0.8573</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0133</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="100">
@@ -21173,10 +20823,10 @@
         <v>3</v>
       </c>
       <c r="G100" t="n">
-        <v>0.9964</v>
+        <v>-0.3262</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3422</v>
+        <v>-0.1303</v>
       </c>
     </row>
     <row r="101">
@@ -21207,10 +20857,10 @@
         <v>3</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.8953</v>
+        <v>-0.9073</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.0034</v>
+        <v>-0.0037</v>
       </c>
     </row>
     <row r="102">
@@ -21241,10 +20891,10 @@
         <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7597</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0032</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="103">
@@ -21275,10 +20925,10 @@
         <v>3</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.9161</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.0021</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="104">
@@ -21309,10 +20959,10 @@
         <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>0.9293</v>
+        <v>0.961</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1366</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="105">
@@ -21343,10 +20993,10 @@
         <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9569</v>
+        <v>0.9795</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1245</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="106">
@@ -21377,10 +21027,10 @@
         <v>3</v>
       </c>
       <c r="G106" t="n">
-        <v>0.1683</v>
+        <v>0.1966</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0057</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="107">
@@ -21411,10 +21061,10 @@
         <v>3</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3584</v>
+        <v>0.2806</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1502</v>
+        <v>0.09180000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -21445,10 +21095,10 @@
         <v>3</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.3585</v>
+        <v>-0.4289</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.0576</v>
+        <v>-0.0698</v>
       </c>
     </row>
     <row r="109">
@@ -21479,10 +21129,10 @@
         <v>3</v>
       </c>
       <c r="G109" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.7328</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0136</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="110">
@@ -21513,10 +21163,10 @@
         <v>3</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.3058</v>
+        <v>-0.3579</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.0444</v>
+        <v>-0.0523</v>
       </c>
     </row>
     <row r="111">
@@ -21547,10 +21197,10 @@
         <v>3</v>
       </c>
       <c r="G111" t="n">
-        <v>0.6519</v>
+        <v>0.6434</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1484</v>
+        <v>0.1437</v>
       </c>
     </row>
     <row r="112">
@@ -21581,10 +21231,10 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8027</v>
+        <v>0.7822</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1056</v>
+        <v>0.08169999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -21615,10 +21265,10 @@
         <v>3</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3944</v>
+        <v>0.3923</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0655</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="114">
@@ -21649,10 +21299,10 @@
         <v>3</v>
       </c>
       <c r="G114" t="n">
-        <v>0.4879</v>
+        <v>0.1362</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0412</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -21683,10 +21333,10 @@
         <v>3</v>
       </c>
       <c r="G115" t="n">
-        <v>0.9442</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1647</v>
+        <v>0.1542</v>
       </c>
     </row>
     <row r="116">
@@ -21717,10 +21367,10 @@
         <v>3</v>
       </c>
       <c r="G116" t="n">
-        <v>0.9393</v>
+        <v>0.968</v>
       </c>
       <c r="H116" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="117">
@@ -21751,10 +21401,10 @@
         <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>0.9522</v>
+        <v>0.923</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1667</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="118">
@@ -21785,10 +21435,10 @@
         <v>3</v>
       </c>
       <c r="G118" t="n">
-        <v>0.5921</v>
+        <v>0.6121</v>
       </c>
       <c r="H118" t="n">
-        <v>0.102</v>
+        <v>0.1093</v>
       </c>
     </row>
     <row r="119">
@@ -21819,10 +21469,10 @@
         <v>3</v>
       </c>
       <c r="G119" t="n">
-        <v>0.8468</v>
+        <v>0.8367</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1352</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="120">
@@ -21853,10 +21503,10 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>0.989</v>
+        <v>0.9883</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1718</v>
+        <v>0.1611</v>
       </c>
     </row>
     <row r="121">
@@ -21887,10 +21537,10 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.9901</v>
+        <v>0.992</v>
       </c>
       <c r="H121" t="n">
-        <v>-1.2285</v>
+        <v>0.4354</v>
       </c>
     </row>
     <row r="122">
@@ -21921,10 +21571,10 @@
         <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.9368</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.8185</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="123">
@@ -21955,10 +21605,10 @@
         <v>3</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.9813</v>
+        <v>0.8474</v>
       </c>
       <c r="H123" t="n">
-        <v>-1.1669</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="124">
@@ -21989,10 +21639,10 @@
         <v>3</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.7192</v>
+        <v>0.9238</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.3328</v>
+        <v>0.6686</v>
       </c>
     </row>
     <row r="125">
@@ -22023,10 +21673,10 @@
         <v>3</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.9865</v>
+        <v>0.8344</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.0319</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="126">
@@ -22057,10 +21707,10 @@
         <v>3</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.9629</v>
+        <v>0.6911</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.024</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="127">
@@ -22091,10 +21741,10 @@
         <v>3</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.3392</v>
       </c>
       <c r="H127" t="n">
-        <v>-1.461</v>
+        <v>-0.5809</v>
       </c>
     </row>
     <row r="128">
@@ -22125,10 +21775,10 @@
         <v>3</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3391</v>
+        <v>0.3517</v>
       </c>
       <c r="H128" t="n">
-        <v>0.067</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="129">
@@ -22159,10 +21809,10 @@
         <v>3</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.9943</v>
+        <v>-0.9996</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.7121</v>
+        <v>-2.2824</v>
       </c>
     </row>
     <row r="130">
@@ -22193,10 +21843,10 @@
         <v>3</v>
       </c>
       <c r="G130" t="n">
-        <v>0.9942</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6884</v>
+        <v>0.7843</v>
       </c>
     </row>
     <row r="131">
@@ -22227,10 +21877,10 @@
         <v>3</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.9122</v>
+        <v>-0.9997</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-1.8322</v>
       </c>
     </row>
     <row r="132">
@@ -22261,10 +21911,10 @@
         <v>3</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.1322</v>
+        <v>-0.1686</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.0027</v>
+        <v>-0.0036</v>
       </c>
     </row>
     <row r="133">
@@ -22295,10 +21945,10 @@
         <v>3</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.7114</v>
+        <v>-0.7433</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.0301</v>
+        <v>-0.0345</v>
       </c>
     </row>
     <row r="134">
@@ -22329,10 +21979,10 @@
         <v>3</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6018</v>
+        <v>0.4898</v>
       </c>
       <c r="H134" t="n">
-        <v>0.5945</v>
+        <v>0.4642</v>
       </c>
     </row>
     <row r="135">
@@ -22839,10 +22489,10 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>0.8858</v>
+        <v>0.9601</v>
       </c>
       <c r="H149" t="n">
-        <v>0.4255</v>
+        <v>0.6832</v>
       </c>
     </row>
     <row r="150">
@@ -22873,10 +22523,10 @@
         <v>3</v>
       </c>
       <c r="G150" t="n">
-        <v>0.9851</v>
+        <v>0.986</v>
       </c>
       <c r="H150" t="n">
-        <v>0.9454</v>
+        <v>0.9447</v>
       </c>
     </row>
     <row r="151">
@@ -22907,10 +22557,10 @@
         <v>3</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9997</v>
       </c>
       <c r="H151" t="n">
-        <v>0.8479</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="152">
@@ -22941,10 +22591,10 @@
         <v>3</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9654</v>
+        <v>0.9699</v>
       </c>
       <c r="H152" t="n">
-        <v>0.6655</v>
+        <v>0.6992</v>
       </c>
     </row>
     <row r="153">
@@ -22975,10 +22625,10 @@
         <v>3</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.0839</v>
+        <v>-0.1233</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.0027</v>
+        <v>-0.0033</v>
       </c>
     </row>
     <row r="154">
@@ -23009,10 +22659,10 @@
         <v>3</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.0745</v>
+        <v>-0.1131</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.0013</v>
+        <v>-0.0014</v>
       </c>
     </row>
     <row r="155">
@@ -23043,10 +22693,10 @@
         <v>3</v>
       </c>
       <c r="G155" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.9232</v>
       </c>
       <c r="H155" t="n">
-        <v>0.031</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="156">
@@ -23077,10 +22727,10 @@
         <v>3</v>
       </c>
       <c r="G156" t="n">
-        <v>0.4169</v>
+        <v>0.7372</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2235</v>
+        <v>0.7969000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -23111,10 +22761,10 @@
         <v>3</v>
       </c>
       <c r="G157" t="n">
-        <v>0.6324</v>
+        <v>0.9183</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1823</v>
+        <v>0.3175</v>
       </c>
     </row>
     <row r="158">
@@ -23145,10 +22795,10 @@
         <v>3</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3241</v>
+        <v>0.9427</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1419</v>
+        <v>0.4923</v>
       </c>
     </row>
     <row r="159">
@@ -23179,10 +22829,10 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>0.6147</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="H159" t="n">
-        <v>0.3277</v>
+        <v>0.6001</v>
       </c>
     </row>
     <row r="160">
@@ -23213,10 +22863,10 @@
         <v>3</v>
       </c>
       <c r="G160" t="n">
-        <v>0.9876</v>
+        <v>0.9719</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0475</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="161">
@@ -23247,10 +22897,10 @@
         <v>3</v>
       </c>
       <c r="G161" t="n">
-        <v>0.5877</v>
+        <v>0.6401</v>
       </c>
       <c r="H161" t="n">
-        <v>0.0191</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="162">
@@ -23281,10 +22931,10 @@
         <v>3</v>
       </c>
       <c r="G162" t="n">
-        <v>0.6005</v>
+        <v>0.4463</v>
       </c>
       <c r="H162" t="n">
-        <v>0.377</v>
+        <v>0.4453</v>
       </c>
     </row>
     <row r="163">
@@ -23315,10 +22965,10 @@
         <v>3</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.3344</v>
+        <v>0.2579</v>
       </c>
       <c r="H163" t="n">
-        <v>-0.103</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="164">
@@ -23349,10 +22999,10 @@
         <v>3</v>
       </c>
       <c r="G164" t="n">
-        <v>-0.9163</v>
+        <v>-0.1933</v>
       </c>
       <c r="H164" t="n">
-        <v>-0.429</v>
+        <v>-0.1251</v>
       </c>
     </row>
     <row r="165">
@@ -23383,10 +23033,10 @@
         <v>3</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.9545</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>-1.0625</v>
+        <v>0.9001</v>
       </c>
     </row>
     <row r="166">
@@ -23417,10 +23067,10 @@
         <v>3</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.996</v>
+        <v>-0.4491</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.3202</v>
+        <v>-0.1963</v>
       </c>
     </row>
     <row r="167">
@@ -23451,10 +23101,10 @@
         <v>3</v>
       </c>
       <c r="G167" t="n">
-        <v>0.6796</v>
+        <v>0.6107</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1041</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="168">
@@ -23485,10 +23135,10 @@
         <v>3</v>
       </c>
       <c r="G168" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.6785</v>
       </c>
       <c r="H168" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="169">
@@ -23519,10 +23169,10 @@
         <v>3</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5868</v>
+        <v>-0.4231</v>
       </c>
       <c r="H169" t="n">
-        <v>0.5272</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="170">
@@ -23553,10 +23203,10 @@
         <v>3</v>
       </c>
       <c r="G170" t="n">
-        <v>0.9996</v>
+        <v>0.9917</v>
       </c>
       <c r="H170" t="n">
-        <v>0.5187</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="171">
@@ -23587,10 +23237,10 @@
         <v>3</v>
       </c>
       <c r="G171" t="n">
-        <v>0.9063</v>
+        <v>-0.6055</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1079</v>
+        <v>-0.0065</v>
       </c>
     </row>
     <row r="172">
@@ -23621,10 +23271,10 @@
         <v>3</v>
       </c>
       <c r="G172" t="n">
-        <v>0.9768</v>
+        <v>-0.8863</v>
       </c>
       <c r="H172" t="n">
-        <v>0.4132</v>
+        <v>-0.0198</v>
       </c>
     </row>
     <row r="173">
@@ -23655,10 +23305,10 @@
         <v>3</v>
       </c>
       <c r="G173" t="n">
-        <v>0.9191</v>
+        <v>-0.4373</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1011</v>
+        <v>-0.0056</v>
       </c>
     </row>
     <row r="174">
@@ -23689,10 +23339,10 @@
         <v>3</v>
       </c>
       <c r="G174" t="n">
-        <v>-0.5992</v>
+        <v>0.6519</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.7188</v>
+        <v>0.3468</v>
       </c>
     </row>
     <row r="175">
@@ -23723,10 +23373,10 @@
         <v>3</v>
       </c>
       <c r="G175" t="n">
-        <v>-0.4268</v>
+        <v>0.8498</v>
       </c>
       <c r="H175" t="n">
-        <v>-0.6732</v>
+        <v>0.4991</v>
       </c>
     </row>
     <row r="176">
@@ -23757,10 +23407,10 @@
         <v>3</v>
       </c>
       <c r="G176" t="n">
-        <v>0.9798</v>
+        <v>0.3789</v>
       </c>
       <c r="H176" t="n">
-        <v>0.4181</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="177">
@@ -23791,10 +23441,10 @@
         <v>3</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4863</v>
+        <v>-0.9847</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0941</v>
+        <v>-0.07539999999999999</v>
       </c>
     </row>
     <row r="178">
@@ -23825,10 +23475,10 @@
         <v>3</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-0.8927</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.0354</v>
+        <v>-0.0409</v>
       </c>
     </row>
     <row r="179">
@@ -23859,10 +23509,10 @@
         <v>3</v>
       </c>
       <c r="G179" t="n">
-        <v>0.9944</v>
+        <v>0.9658</v>
       </c>
       <c r="H179" t="n">
-        <v>0.0756</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="180">
@@ -23893,10 +23543,10 @@
         <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>-0.9381</v>
+        <v>-0.9968</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.0371</v>
+        <v>-0.0457</v>
       </c>
     </row>
     <row r="181">
@@ -23927,10 +23577,10 @@
         <v>3</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9625</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.4428</v>
+        <v>-0.4623</v>
       </c>
     </row>
     <row r="182">
@@ -23961,10 +23611,10 @@
         <v>3</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.8861</v>
+        <v>-0.9708</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.3268</v>
+        <v>-0.3785</v>
       </c>
     </row>
     <row r="183">
@@ -23995,10 +23645,10 @@
         <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4536</v>
+        <v>0.0716</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0151</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="184">
@@ -24029,10 +23679,10 @@
         <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.9849</v>
+        <v>0.8309</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.1589</v>
+        <v>0.4988</v>
       </c>
     </row>
     <row r="185">
@@ -24063,10 +23713,10 @@
         <v>3</v>
       </c>
       <c r="G185" t="n">
-        <v>0.239</v>
+        <v>-0.9785</v>
       </c>
       <c r="H185" t="n">
-        <v>0.3061</v>
+        <v>-0.8446</v>
       </c>
     </row>
     <row r="186">
@@ -24097,10 +23747,10 @@
         <v>3</v>
       </c>
       <c r="G186" t="n">
-        <v>-0.9979</v>
+        <v>-0.7612</v>
       </c>
       <c r="H186" t="n">
-        <v>-0.4554</v>
+        <v>-0.3477</v>
       </c>
     </row>
     <row r="187">
@@ -24131,10 +23781,10 @@
         <v>3</v>
       </c>
       <c r="G187" t="n">
-        <v>0.028</v>
+        <v>-0.9712</v>
       </c>
       <c r="H187" t="n">
-        <v>0.035</v>
+        <v>-1.8993</v>
       </c>
     </row>
     <row r="188">
@@ -24165,10 +23815,10 @@
         <v>3</v>
       </c>
       <c r="G188" t="n">
-        <v>0.5513</v>
+        <v>0.9792</v>
       </c>
       <c r="H188" t="n">
-        <v>0.2378</v>
+        <v>0.2529</v>
       </c>
     </row>
     <row r="189">
@@ -24199,10 +23849,10 @@
         <v>3</v>
       </c>
       <c r="G189" t="n">
-        <v>0.4682</v>
+        <v>0.8823</v>
       </c>
       <c r="H189" t="n">
-        <v>0.2577</v>
+        <v>0.3937</v>
       </c>
     </row>
     <row r="190">
@@ -24233,10 +23883,10 @@
         <v>3</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.998</v>
+        <v>-0.9979</v>
       </c>
       <c r="H190" t="n">
-        <v>-0.1996</v>
+        <v>-0.177</v>
       </c>
     </row>
     <row r="191">
@@ -24267,10 +23917,10 @@
         <v>10</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.2904</v>
+        <v>-0.3527</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.117</v>
+        <v>-0.1187</v>
       </c>
     </row>
     <row r="192">
@@ -24301,10 +23951,10 @@
         <v>10</v>
       </c>
       <c r="G192" t="n">
-        <v>0.3354</v>
+        <v>0.3403</v>
       </c>
       <c r="H192" t="n">
-        <v>0.121</v>
+        <v>0.1239</v>
       </c>
     </row>
     <row r="193">
@@ -24335,10 +23985,10 @@
         <v>10</v>
       </c>
       <c r="G193" t="n">
-        <v>0.2904</v>
+        <v>0.3648</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1762</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="194">
@@ -24369,10 +24019,10 @@
         <v>10</v>
       </c>
       <c r="G194" t="n">
-        <v>0.3741</v>
+        <v>0.3643</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0834</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -24403,10 +24053,10 @@
         <v>10</v>
       </c>
       <c r="G195" t="n">
-        <v>-0.1333</v>
+        <v>0.0596</v>
       </c>
       <c r="H195" t="n">
-        <v>-0.0027</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="196">
@@ -24437,10 +24087,10 @@
         <v>10</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.1778</v>
+        <v>-0.0111</v>
       </c>
       <c r="H196" t="n">
-        <v>-0.0016</v>
+        <v>-0.0001</v>
       </c>
     </row>
     <row r="197">
@@ -24471,10 +24121,10 @@
         <v>10</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3047</v>
+        <v>0.3483</v>
       </c>
       <c r="H197" t="n">
-        <v>0.2346</v>
+        <v>0.2835</v>
       </c>
     </row>
     <row r="198">
@@ -24505,10 +24155,10 @@
         <v>10</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.8244</v>
+        <v>-0.8878</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.0027</v>
+        <v>-1.0483</v>
       </c>
     </row>
     <row r="199">
@@ -24539,10 +24189,10 @@
         <v>10</v>
       </c>
       <c r="G199" t="n">
-        <v>0.8919</v>
+        <v>0.925</v>
       </c>
       <c r="H199" t="n">
-        <v>0.4334</v>
+        <v>0.4875</v>
       </c>
     </row>
     <row r="200">
@@ -24573,10 +24223,10 @@
         <v>10</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.7219</v>
+        <v>-0.7912</v>
       </c>
       <c r="H200" t="n">
-        <v>-0.4582</v>
+        <v>-0.5775</v>
       </c>
     </row>
     <row r="201">
@@ -24607,10 +24257,10 @@
         <v>10</v>
       </c>
       <c r="G201" t="n">
-        <v>0.8488</v>
+        <v>0.8938</v>
       </c>
       <c r="H201" t="n">
-        <v>0.3082</v>
+        <v>0.3669</v>
       </c>
     </row>
     <row r="202">
@@ -24641,10 +24291,10 @@
         <v>10</v>
       </c>
       <c r="G202" t="n">
-        <v>0.3454</v>
+        <v>0.4767</v>
       </c>
       <c r="H202" t="n">
-        <v>0.0247</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="203">
@@ -24675,10 +24325,10 @@
         <v>10</v>
       </c>
       <c r="G203" t="n">
-        <v>0.2913</v>
+        <v>0.4608</v>
       </c>
       <c r="H203" t="n">
-        <v>0.0117</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="204">
@@ -24709,10 +24359,10 @@
         <v>10</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.1229</v>
+        <v>-0.3365</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.094</v>
+        <v>-0.2897</v>
       </c>
     </row>
     <row r="205">
@@ -24743,10 +24393,10 @@
         <v>10</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0434</v>
+        <v>0.0853</v>
       </c>
       <c r="H205" t="n">
-        <v>0.0331</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -24777,10 +24427,10 @@
         <v>10</v>
       </c>
       <c r="G206" t="n">
-        <v>0.4012</v>
+        <v>0.4597</v>
       </c>
       <c r="H206" t="n">
-        <v>0.3973</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="207">
@@ -24811,10 +24461,10 @@
         <v>10</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.256</v>
+        <v>0.1119</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.1208</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="208">
@@ -24845,10 +24495,10 @@
         <v>10</v>
       </c>
       <c r="G208" t="n">
-        <v>0.381</v>
+        <v>0.4427</v>
       </c>
       <c r="H208" t="n">
-        <v>0.2759</v>
+        <v>0.2986</v>
       </c>
     </row>
     <row r="209">
@@ -24879,10 +24529,10 @@
         <v>10</v>
       </c>
       <c r="G209" t="n">
-        <v>0.5171</v>
+        <v>0.5184</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0212</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="210">
@@ -24913,10 +24563,10 @@
         <v>10</v>
       </c>
       <c r="G210" t="n">
-        <v>0.4242</v>
+        <v>0.4286</v>
       </c>
       <c r="H210" t="n">
-        <v>0.0077</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="211">
@@ -24947,10 +24597,10 @@
         <v>10</v>
       </c>
       <c r="G211" t="n">
-        <v>-0.665</v>
+        <v>-0.5326</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.1119</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="212">
@@ -24981,10 +24631,10 @@
         <v>10</v>
       </c>
       <c r="G212" t="n">
-        <v>0.6362</v>
+        <v>0.8975</v>
       </c>
       <c r="H212" t="n">
-        <v>0.6287</v>
+        <v>0.8901</v>
       </c>
     </row>
     <row r="213">
@@ -25015,10 +24665,10 @@
         <v>10</v>
       </c>
       <c r="G213" t="n">
-        <v>0.9778</v>
+        <v>0.978</v>
       </c>
       <c r="H213" t="n">
-        <v>0.8907</v>
+        <v>0.8917</v>
       </c>
     </row>
     <row r="214">
@@ -25049,10 +24699,10 @@
         <v>10</v>
       </c>
       <c r="G214" t="n">
-        <v>0.8562</v>
+        <v>0.9829</v>
       </c>
       <c r="H214" t="n">
-        <v>0.757</v>
+        <v>0.9116</v>
       </c>
     </row>
     <row r="215">
@@ -25083,10 +24733,10 @@
         <v>10</v>
       </c>
       <c r="G215" t="n">
-        <v>0.9457</v>
+        <v>0.9477</v>
       </c>
       <c r="H215" t="n">
-        <v>0.8447</v>
+        <v>0.8556</v>
       </c>
     </row>
     <row r="216">
@@ -25117,10 +24767,10 @@
         <v>10</v>
       </c>
       <c r="G216" t="n">
-        <v>0.8502</v>
+        <v>0.8462</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0389</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="217">
@@ -25151,10 +24801,10 @@
         <v>10</v>
       </c>
       <c r="G217" t="n">
-        <v>0.9266</v>
+        <v>0.9071</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0164</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="218">
@@ -25185,10 +24835,10 @@
         <v>10</v>
       </c>
       <c r="G218" t="n">
-        <v>0.6246</v>
+        <v>0.7212</v>
       </c>
       <c r="H218" t="n">
-        <v>0.5568</v>
+        <v>0.6593</v>
       </c>
     </row>
     <row r="219">
@@ -25219,10 +24869,10 @@
         <v>10</v>
       </c>
       <c r="G219" t="n">
-        <v>0.8068</v>
+        <v>0.8751</v>
       </c>
       <c r="H219" t="n">
-        <v>0.7342</v>
+        <v>0.8852</v>
       </c>
     </row>
     <row r="220">
@@ -25253,10 +24903,10 @@
         <v>10</v>
       </c>
       <c r="G220" t="n">
-        <v>0.8692</v>
+        <v>0.9206</v>
       </c>
       <c r="H220" t="n">
-        <v>0.764</v>
+        <v>0.7958</v>
       </c>
     </row>
     <row r="221">
@@ -25287,10 +24937,10 @@
         <v>10</v>
       </c>
       <c r="G221" t="n">
-        <v>0.6955</v>
+        <v>0.9556</v>
       </c>
       <c r="H221" t="n">
-        <v>0.6878</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="222">
@@ -25321,10 +24971,10 @@
         <v>10</v>
       </c>
       <c r="G222" t="n">
-        <v>0.8149</v>
+        <v>0.9022</v>
       </c>
       <c r="H222" t="n">
-        <v>0.7833</v>
+        <v>0.8647</v>
       </c>
     </row>
     <row r="223">
@@ -25355,10 +25005,10 @@
         <v>10</v>
       </c>
       <c r="G223" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7617</v>
       </c>
       <c r="H223" t="n">
-        <v>0.0234</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="224">
@@ -25389,10 +25039,10 @@
         <v>10</v>
       </c>
       <c r="G224" t="n">
-        <v>0.8496</v>
+        <v>0.8359</v>
       </c>
       <c r="H224" t="n">
-        <v>0.0101</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -25423,10 +25073,10 @@
         <v>10</v>
       </c>
       <c r="G225" t="n">
-        <v>0.2664</v>
+        <v>0.363</v>
       </c>
       <c r="H225" t="n">
-        <v>0.2853</v>
+        <v>0.3691</v>
       </c>
     </row>
     <row r="226">
@@ -25457,10 +25107,10 @@
         <v>10</v>
       </c>
       <c r="G226" t="n">
-        <v>0.3443</v>
+        <v>0.855</v>
       </c>
       <c r="H226" t="n">
-        <v>0.2608</v>
+        <v>0.8617</v>
       </c>
     </row>
     <row r="227">
@@ -25491,10 +25141,10 @@
         <v>10</v>
       </c>
       <c r="G227" t="n">
-        <v>0.9144</v>
+        <v>0.9191</v>
       </c>
       <c r="H227" t="n">
-        <v>0.8914</v>
+        <v>0.9013</v>
       </c>
     </row>
     <row r="228">
@@ -25525,10 +25175,10 @@
         <v>10</v>
       </c>
       <c r="G228" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.9396</v>
       </c>
       <c r="H228" t="n">
-        <v>0.6903</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="229">
@@ -25559,10 +25209,10 @@
         <v>10</v>
       </c>
       <c r="G229" t="n">
-        <v>0.9049</v>
+        <v>0.9177</v>
       </c>
       <c r="H229" t="n">
-        <v>0.7679</v>
+        <v>0.8036</v>
       </c>
     </row>
     <row r="230">
@@ -25593,10 +25243,10 @@
         <v>10</v>
       </c>
       <c r="G230" t="n">
-        <v>0.7593</v>
+        <v>0.8003</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0211</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="231">
@@ -25627,10 +25277,10 @@
         <v>10</v>
       </c>
       <c r="G231" t="n">
-        <v>0.847</v>
+        <v>0.8666</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0086</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="232">
@@ -25661,10 +25311,10 @@
         <v>10</v>
       </c>
       <c r="G232" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0257</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="233">
@@ -25933,10 +25583,10 @@
         <v>10</v>
       </c>
       <c r="G240" t="n">
-        <v>-0.0696</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.0169</v>
+        <v>-0.0151</v>
       </c>
     </row>
     <row r="241">
@@ -25967,10 +25617,10 @@
         <v>10</v>
       </c>
       <c r="G241" t="n">
-        <v>0.8144</v>
+        <v>0.7996</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0263</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="242">
@@ -26001,10 +25651,10 @@
         <v>10</v>
       </c>
       <c r="G242" t="n">
-        <v>0.4873</v>
+        <v>0.3952</v>
       </c>
       <c r="H242" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="243">
@@ -26035,10 +25685,10 @@
         <v>10</v>
       </c>
       <c r="G243" t="n">
-        <v>0.8102</v>
+        <v>0.7879</v>
       </c>
       <c r="H243" t="n">
-        <v>0.0216</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="244">
@@ -26069,10 +25719,10 @@
         <v>10</v>
       </c>
       <c r="G244" t="n">
-        <v>-0.1414</v>
+        <v>-0.0616</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.0052</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="245">
@@ -26103,10 +25753,10 @@
         <v>10</v>
       </c>
       <c r="G245" t="n">
-        <v>-0.1126</v>
+        <v>0.2014</v>
       </c>
       <c r="H245" t="n">
-        <v>-0.0013</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="246">
@@ -26137,10 +25787,10 @@
         <v>10</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0312</v>
+        <v>-0.0688</v>
       </c>
       <c r="H246" t="n">
-        <v>0.0054</v>
+        <v>-0.0112</v>
       </c>
     </row>
     <row r="247">
@@ -26171,10 +25821,10 @@
         <v>10</v>
       </c>
       <c r="G247" t="n">
-        <v>0.7544</v>
+        <v>0.6664</v>
       </c>
       <c r="H247" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5022</v>
       </c>
     </row>
     <row r="248">
@@ -26205,10 +25855,10 @@
         <v>10</v>
       </c>
       <c r="G248" t="n">
-        <v>0.5377</v>
+        <v>0.5617</v>
       </c>
       <c r="H248" t="n">
-        <v>0.004</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="249">
@@ -26239,10 +25889,10 @@
         <v>10</v>
       </c>
       <c r="G249" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H249" t="n">
-        <v>0.023</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="250">
@@ -26273,7 +25923,7 @@
         <v>10</v>
       </c>
       <c r="G250" t="n">
-        <v>0.6024</v>
+        <v>0.6299</v>
       </c>
       <c r="H250" t="n">
         <v>0.0042</v>
@@ -26307,10 +25957,10 @@
         <v>10</v>
       </c>
       <c r="G251" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="H251" t="n">
-        <v>0.0377</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="252">
@@ -26341,10 +25991,10 @@
         <v>10</v>
       </c>
       <c r="G252" t="n">
-        <v>0.2978</v>
+        <v>-0.1039</v>
       </c>
       <c r="H252" t="n">
-        <v>0.0036</v>
+        <v>-0.0012</v>
       </c>
     </row>
     <row r="253">
@@ -26375,10 +26025,10 @@
         <v>10</v>
       </c>
       <c r="G253" t="n">
-        <v>-0.1306</v>
+        <v>-0.1915</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.01</v>
+        <v>-0.0141</v>
       </c>
     </row>
     <row r="254">
@@ -26409,10 +26059,10 @@
         <v>10</v>
       </c>
       <c r="G254" t="n">
-        <v>0.7995</v>
+        <v>0.7594</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1227</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="255">
@@ -26443,10 +26093,10 @@
         <v>10</v>
       </c>
       <c r="G255" t="n">
-        <v>0.7345</v>
+        <v>0.7442</v>
       </c>
       <c r="H255" t="n">
-        <v>0.7138</v>
+        <v>0.7613</v>
       </c>
     </row>
     <row r="256">
@@ -26477,10 +26127,10 @@
         <v>10</v>
       </c>
       <c r="G256" t="n">
-        <v>0.7976</v>
+        <v>0.8007</v>
       </c>
       <c r="H256" t="n">
-        <v>0.4027</v>
+        <v>0.3165</v>
       </c>
     </row>
     <row r="257">
@@ -26511,10 +26161,10 @@
         <v>10</v>
       </c>
       <c r="G257" t="n">
-        <v>0.7612</v>
+        <v>0.7714</v>
       </c>
       <c r="H257" t="n">
-        <v>0.2252</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="258">
@@ -26545,10 +26195,10 @@
         <v>10</v>
       </c>
       <c r="G258" t="n">
-        <v>0.5467</v>
+        <v>0.4991</v>
       </c>
       <c r="H258" t="n">
-        <v>0.041</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="259">
@@ -26579,10 +26229,10 @@
         <v>10</v>
       </c>
       <c r="G259" t="n">
-        <v>0.7496</v>
+        <v>0.7274</v>
       </c>
       <c r="H259" t="n">
-        <v>0.0225</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="260">
@@ -26613,10 +26263,10 @@
         <v>10</v>
       </c>
       <c r="G260" t="n">
-        <v>0.483</v>
+        <v>0.4652</v>
       </c>
       <c r="H260" t="n">
-        <v>0.0299</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="261">
@@ -26647,10 +26297,10 @@
         <v>10</v>
       </c>
       <c r="G261" t="n">
-        <v>0.3763</v>
+        <v>0.4003</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1103</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="262">
@@ -26681,10 +26331,10 @@
         <v>10</v>
       </c>
       <c r="G262" t="n">
-        <v>0.6816</v>
+        <v>0.759</v>
       </c>
       <c r="H262" t="n">
-        <v>0.5755</v>
+        <v>0.5753</v>
       </c>
     </row>
     <row r="263">
@@ -26715,10 +26365,10 @@
         <v>10</v>
       </c>
       <c r="G263" t="n">
-        <v>0.6036</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="H263" t="n">
-        <v>0.6176</v>
+        <v>0.6532</v>
       </c>
     </row>
     <row r="264">
@@ -26749,10 +26399,10 @@
         <v>10</v>
       </c>
       <c r="G264" t="n">
-        <v>0.7245</v>
+        <v>0.7974</v>
       </c>
       <c r="H264" t="n">
-        <v>0.3198</v>
+        <v>0.2946</v>
       </c>
     </row>
     <row r="265">
@@ -26783,10 +26433,10 @@
         <v>10</v>
       </c>
       <c r="G265" t="n">
-        <v>0.5823</v>
+        <v>0.5728</v>
       </c>
       <c r="H265" t="n">
-        <v>0.2089</v>
+        <v>0.1593</v>
       </c>
     </row>
     <row r="266">
@@ -26817,10 +26467,10 @@
         <v>10</v>
       </c>
       <c r="G266" t="n">
-        <v>0.6509</v>
+        <v>0.6575</v>
       </c>
       <c r="H266" t="n">
-        <v>0.0813</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="267">
@@ -26851,10 +26501,10 @@
         <v>10</v>
       </c>
       <c r="G267" t="n">
-        <v>0.2749</v>
+        <v>0.4046</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1069</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="268">
@@ -26885,10 +26535,10 @@
         <v>10</v>
       </c>
       <c r="G268" t="n">
-        <v>0.2701</v>
+        <v>0.2264</v>
       </c>
       <c r="H268" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="269">
@@ -26919,10 +26569,10 @@
         <v>10</v>
       </c>
       <c r="G269" t="n">
-        <v>0.4662</v>
+        <v>0.3693</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1872</v>
+        <v>0.1445</v>
       </c>
     </row>
     <row r="270">
@@ -26953,10 +26603,10 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>0.3837</v>
+        <v>0.2151</v>
       </c>
       <c r="H270" t="n">
-        <v>0.324</v>
+        <v>0.2091</v>
       </c>
     </row>
     <row r="271">
@@ -26987,10 +26637,10 @@
         <v>10</v>
       </c>
       <c r="G271" t="n">
-        <v>0.5415</v>
+        <v>0.4553</v>
       </c>
       <c r="H271" t="n">
-        <v>0.0727</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="272">
@@ -27021,10 +26671,10 @@
         <v>10</v>
       </c>
       <c r="G272" t="n">
-        <v>-0.1565</v>
+        <v>-0.213</v>
       </c>
       <c r="H272" t="n">
-        <v>-0.0261</v>
+        <v>-0.0338</v>
       </c>
     </row>
     <row r="273">
@@ -27055,10 +26705,10 @@
         <v>10</v>
       </c>
       <c r="G273" t="n">
-        <v>-0.1493</v>
+        <v>-0.1755</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.0098</v>
+        <v>-0.0113</v>
       </c>
     </row>
     <row r="274">
@@ -27089,10 +26739,10 @@
         <v>10</v>
       </c>
       <c r="G274" t="n">
-        <v>0.5172</v>
+        <v>0.515</v>
       </c>
       <c r="H274" t="n">
-        <v>0.0322</v>
+        <v>0.0321</v>
       </c>
     </row>
   </sheetData>
